--- a/report-promnite2026.xlsx
+++ b/report-promnite2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3049" uniqueCount="2464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3051" uniqueCount="2466">
   <si>
     <t>No</t>
   </si>
@@ -6028,6 +6028,9 @@
     </r>
   </si>
   <si>
+    <t>gaada</t>
+  </si>
+  <si>
     <t>https://udr.reddonedigital.com/ClaytonKenjiroEmanuell/Promnite2026/85409/398</t>
   </si>
   <si>
@@ -7016,6 +7019,9 @@
       </rPr>
       <t>12H</t>
     </r>
+  </si>
+  <si>
+    <t>.</t>
   </si>
   <si>
     <t>https://udr.reddonedigital.com/LivineQuineilla/Promnite2026/85456/398</t>
@@ -10151,25 +10157,18 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -10474,7 +10473,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="13" width="10.0"/>
+    <col customWidth="1" min="1" max="13" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -14411,7 +14410,7 @@
         <v>639</v>
       </c>
       <c r="J146" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="K146">
         <v>0.0</v>
@@ -15899,10 +15898,10 @@
         <v>897</v>
       </c>
       <c r="J197" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K197">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M197" t="s">
         <v>898</v>
@@ -16366,10 +16365,10 @@
         <v>978</v>
       </c>
       <c r="J213" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K213">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M213" t="s">
         <v>979</v>
@@ -16449,7 +16448,7 @@
       <c r="F216">
         <v>6.285156514035E12</v>
       </c>
-      <c r="G216" s="5" t="s">
+      <c r="G216" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J216" t="s">
@@ -16478,7 +16477,7 @@
       <c r="F217">
         <v>6.282310876592E12</v>
       </c>
-      <c r="G217" s="5" t="s">
+      <c r="G217" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J217" t="s">
@@ -16507,7 +16506,7 @@
       <c r="F218">
         <v>6.28113030825E11</v>
       </c>
-      <c r="G218" s="5" t="s">
+      <c r="G218" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J218" t="s">
@@ -16536,7 +16535,7 @@
       <c r="F219">
         <v>6.2811518513E10</v>
       </c>
-      <c r="G219" s="5" t="s">
+      <c r="G219" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J219" t="s">
@@ -16565,7 +16564,7 @@
       <c r="F220">
         <v>6.2811782008E10</v>
       </c>
-      <c r="G220" s="5" t="s">
+      <c r="G220" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J220" t="s">
@@ -16594,7 +16593,7 @@
       <c r="F221">
         <v>6.282143100573E12</v>
       </c>
-      <c r="G221" s="5" t="s">
+      <c r="G221" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J221" t="s">
@@ -16623,7 +16622,7 @@
       <c r="F222">
         <v>6.282192604763E12</v>
       </c>
-      <c r="G222" s="5" t="s">
+      <c r="G222" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J222" t="s">
@@ -16652,7 +16651,7 @@
       <c r="F223">
         <v>6.28521608875E12</v>
       </c>
-      <c r="G223" s="5" t="s">
+      <c r="G223" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J223" t="s">
@@ -16681,7 +16680,7 @@
       <c r="F224">
         <v>6.288213358681E12</v>
       </c>
-      <c r="G224" s="5" t="s">
+      <c r="G224" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J224" t="s">
@@ -16710,11 +16709,11 @@
       <c r="F225">
         <v>6.28219033506E12</v>
       </c>
-      <c r="G225" s="5" t="s">
+      <c r="G225" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J225" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="K225">
         <v>0.0</v>
@@ -16739,7 +16738,7 @@
       <c r="F226">
         <v>6.28123012625E12</v>
       </c>
-      <c r="G226" s="5" t="s">
+      <c r="G226" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J226" t="s">
@@ -16768,14 +16767,14 @@
       <c r="F227">
         <v>6.282143005918E12</v>
       </c>
-      <c r="G227" s="5" t="s">
+      <c r="G227" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J227" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K227">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M227" t="s">
         <v>1038</v>
@@ -16797,7 +16796,7 @@
       <c r="F228">
         <v>6.2816551118E10</v>
       </c>
-      <c r="G228" s="5" t="s">
+      <c r="G228" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J228" t="s">
@@ -16826,7 +16825,7 @@
       <c r="F229">
         <v>6.282231363819E12</v>
       </c>
-      <c r="G229" s="5" t="s">
+      <c r="G229" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J229" t="s">
@@ -16855,7 +16854,7 @@
       <c r="F230">
         <v>6.282244587779E12</v>
       </c>
-      <c r="G230" s="5" t="s">
+      <c r="G230" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J230" t="s">
@@ -16884,7 +16883,7 @@
       <c r="F231">
         <v>6.281217367118E12</v>
       </c>
-      <c r="G231" s="5" t="s">
+      <c r="G231" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J231" t="s">
@@ -16913,7 +16912,7 @@
       <c r="F232">
         <v>6.2895809179318E13</v>
       </c>
-      <c r="G232" s="5" t="s">
+      <c r="G232" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J232" t="s">
@@ -16942,7 +16941,7 @@
       <c r="F233">
         <v>6.285755320331E12</v>
       </c>
-      <c r="G233" s="5" t="s">
+      <c r="G233" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J233" t="s">
@@ -16971,7 +16970,7 @@
       <c r="F234">
         <v>6.28225549663E12</v>
       </c>
-      <c r="G234" s="5" t="s">
+      <c r="G234" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J234" t="s">
@@ -17000,7 +16999,7 @@
       <c r="F235">
         <v>6.281280645537E12</v>
       </c>
-      <c r="G235" s="5" t="s">
+      <c r="G235" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J235" t="s">
@@ -17029,7 +17028,7 @@
       <c r="F236">
         <v>6.281248185994E12</v>
       </c>
-      <c r="G236" s="5" t="s">
+      <c r="G236" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J236" t="s">
@@ -17058,7 +17057,7 @@
       <c r="F237">
         <v>6.281339948282E12</v>
       </c>
-      <c r="G237" s="5" t="s">
+      <c r="G237" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J237" t="s">
@@ -17087,7 +17086,7 @@
       <c r="F238">
         <v>6.287860367988E12</v>
       </c>
-      <c r="G238" s="5" t="s">
+      <c r="G238" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J238" t="s">
@@ -17116,7 +17115,7 @@
       <c r="F239">
         <v>6.285173050836E12</v>
       </c>
-      <c r="G239" s="5" t="s">
+      <c r="G239" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J239" t="s">
@@ -17148,7 +17147,7 @@
       <c r="F240">
         <v>6.281233336557E12</v>
       </c>
-      <c r="G240" s="5" t="s">
+      <c r="G240" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J240" t="s">
@@ -17177,7 +17176,7 @@
       <c r="F241">
         <v>6.2895416080683E13</v>
       </c>
-      <c r="G241" s="5" t="s">
+      <c r="G241" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J241" t="s">
@@ -17206,7 +17205,7 @@
       <c r="F242">
         <v>6.28951379579E12</v>
       </c>
-      <c r="G242" s="5" t="s">
+      <c r="G242" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J242" t="s">
@@ -17235,7 +17234,7 @@
       <c r="F243">
         <v>6.282155496655E12</v>
       </c>
-      <c r="G243" s="5" t="s">
+      <c r="G243" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J243" t="s">
@@ -17264,7 +17263,7 @@
       <c r="F244">
         <v>6.282110227922E12</v>
       </c>
-      <c r="G244" s="5" t="s">
+      <c r="G244" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J244" t="s">
@@ -17293,7 +17292,7 @@
       <c r="F245">
         <v>6.287764505684E12</v>
       </c>
-      <c r="G245" s="5" t="s">
+      <c r="G245" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J245" t="s">
@@ -17322,7 +17321,7 @@
       <c r="F246">
         <v>6.281233200808E12</v>
       </c>
-      <c r="G246" s="5" t="s">
+      <c r="G246" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J246" t="s">
@@ -17351,7 +17350,7 @@
       <c r="F247">
         <v>6.2895396766399E13</v>
       </c>
-      <c r="G247" s="5" t="s">
+      <c r="G247" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J247" t="s">
@@ -17383,7 +17382,7 @@
       <c r="F248">
         <v>6.282143882989E12</v>
       </c>
-      <c r="G248" s="5" t="s">
+      <c r="G248" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J248" t="s">
@@ -17412,7 +17411,7 @@
       <c r="F249">
         <v>6.281241893603E12</v>
       </c>
-      <c r="G249" s="5" t="s">
+      <c r="G249" s="4" t="s">
         <v>993</v>
       </c>
       <c r="J249" t="s">
@@ -18054,10 +18053,10 @@
         <v>1237</v>
       </c>
       <c r="J271" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K271">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M271" t="s">
         <v>1238</v>
@@ -18315,10 +18314,10 @@
         <v>1282</v>
       </c>
       <c r="J280" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K280">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M280" t="s">
         <v>1283</v>
@@ -18430,7 +18429,7 @@
       <c r="F284">
         <v>6.283834452257E12</v>
       </c>
-      <c r="G284" s="5" t="s">
+      <c r="G284" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J284" t="s">
@@ -18459,7 +18458,7 @@
       <c r="F285">
         <v>6.285822361897E12</v>
       </c>
-      <c r="G285" s="5" t="s">
+      <c r="G285" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J285" t="s">
@@ -18488,7 +18487,7 @@
       <c r="F286">
         <v>6.282134819977E12</v>
       </c>
-      <c r="G286" s="5" t="s">
+      <c r="G286" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J286" t="s">
@@ -18517,7 +18516,7 @@
       <c r="F287">
         <v>6.281287738554E12</v>
       </c>
-      <c r="G287" s="5" t="s">
+      <c r="G287" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J287" t="s">
@@ -18546,7 +18545,7 @@
       <c r="F288">
         <v>6.283866620555E12</v>
       </c>
-      <c r="G288" s="5" t="s">
+      <c r="G288" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J288" t="s">
@@ -18575,7 +18574,7 @@
       <c r="F289">
         <v>6.282143215192E12</v>
       </c>
-      <c r="G289" s="5" t="s">
+      <c r="G289" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J289" t="s">
@@ -18604,7 +18603,7 @@
       <c r="F290">
         <v>6.28137946785E12</v>
       </c>
-      <c r="G290" s="5" t="s">
+      <c r="G290" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J290" t="s">
@@ -18633,7 +18632,7 @@
       <c r="F291">
         <v>6.285856611856E12</v>
       </c>
-      <c r="G291" s="5" t="s">
+      <c r="G291" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J291" t="s">
@@ -18662,7 +18661,7 @@
       <c r="F292">
         <v>6.282247300033E12</v>
       </c>
-      <c r="G292" s="5" t="s">
+      <c r="G292" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J292" t="s">
@@ -18691,7 +18690,7 @@
       <c r="F293">
         <v>6.281231184402E12</v>
       </c>
-      <c r="G293" s="5" t="s">
+      <c r="G293" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J293" t="s">
@@ -18720,7 +18719,7 @@
       <c r="F294">
         <v>6.282229869769E12</v>
       </c>
-      <c r="G294" s="5" t="s">
+      <c r="G294" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J294" t="s">
@@ -18749,7 +18748,7 @@
       <c r="F295">
         <v>6.281345424703E12</v>
       </c>
-      <c r="G295" s="5" t="s">
+      <c r="G295" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J295" t="s">
@@ -18781,7 +18780,7 @@
       <c r="F296">
         <v>6.281252626068E12</v>
       </c>
-      <c r="G296" s="5" t="s">
+      <c r="G296" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J296" t="s">
@@ -18810,7 +18809,7 @@
       <c r="F297">
         <v>6.28123580626E11</v>
       </c>
-      <c r="G297" s="5" t="s">
+      <c r="G297" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J297" t="s">
@@ -18839,7 +18838,7 @@
       <c r="F298">
         <v>6.282271534588E12</v>
       </c>
-      <c r="G298" s="5" t="s">
+      <c r="G298" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J298" t="s">
@@ -18868,7 +18867,7 @@
       <c r="F299">
         <v>6.281230444281E12</v>
       </c>
-      <c r="G299" s="5" t="s">
+      <c r="G299" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J299" t="s">
@@ -18897,7 +18896,7 @@
       <c r="F300">
         <v>6.282140536689E12</v>
       </c>
-      <c r="G300" s="5" t="s">
+      <c r="G300" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J300" t="s">
@@ -18929,7 +18928,7 @@
       <c r="F301">
         <v>6.282155257771E12</v>
       </c>
-      <c r="G301" s="5" t="s">
+      <c r="G301" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J301" t="s">
@@ -18958,7 +18957,7 @@
       <c r="F302">
         <v>6.28131306073E12</v>
       </c>
-      <c r="G302" s="5" t="s">
+      <c r="G302" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J302" t="s">
@@ -18987,7 +18986,7 @@
       <c r="F303">
         <v>6.282238572513E12</v>
       </c>
-      <c r="G303" s="5" t="s">
+      <c r="G303" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J303" t="s">
@@ -19016,7 +19015,7 @@
       <c r="F304">
         <v>6.281231634929E12</v>
       </c>
-      <c r="G304" s="5" t="s">
+      <c r="G304" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J304" t="s">
@@ -19045,7 +19044,7 @@
       <c r="F305">
         <v>6.282253040847E12</v>
       </c>
-      <c r="G305" s="5" t="s">
+      <c r="G305" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J305" t="s">
@@ -19074,7 +19073,7 @@
       <c r="F306">
         <v>6.28135888288E12</v>
       </c>
-      <c r="G306" s="5" t="s">
+      <c r="G306" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J306" t="s">
@@ -19103,7 +19102,7 @@
       <c r="F307">
         <v>6.2895353001006E13</v>
       </c>
-      <c r="G307" s="5" t="s">
+      <c r="G307" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J307" t="s">
@@ -19132,7 +19131,7 @@
       <c r="F308">
         <v>6.282245336478E12</v>
       </c>
-      <c r="G308" s="5" t="s">
+      <c r="G308" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J308" t="s">
@@ -19161,7 +19160,7 @@
       <c r="F309">
         <v>6.281259586873E12</v>
       </c>
-      <c r="G309" s="5" t="s">
+      <c r="G309" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J309" t="s">
@@ -19190,7 +19189,7 @@
       <c r="F310">
         <v>6.28121660528E12</v>
       </c>
-      <c r="G310" s="5" t="s">
+      <c r="G310" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J310" t="s">
@@ -19219,7 +19218,7 @@
       <c r="F311">
         <v>6.282310919736E12</v>
       </c>
-      <c r="G311" s="5" t="s">
+      <c r="G311" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J311" t="s">
@@ -19248,7 +19247,7 @@
       <c r="F312">
         <v>6.282139127577E12</v>
       </c>
-      <c r="G312" s="5" t="s">
+      <c r="G312" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J312" t="s">
@@ -19277,7 +19276,7 @@
       <c r="F313">
         <v>6.2812354222E12</v>
       </c>
-      <c r="G313" s="5" t="s">
+      <c r="G313" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J313" t="s">
@@ -19306,7 +19305,7 @@
       <c r="F314">
         <v>6.28233723683E12</v>
       </c>
-      <c r="G314" s="5" t="s">
+      <c r="G314" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J314" t="s">
@@ -19335,7 +19334,7 @@
       <c r="F315">
         <v>6.281937688899E12</v>
       </c>
-      <c r="G315" s="5" t="s">
+      <c r="G315" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J315" t="s">
@@ -19364,7 +19363,7 @@
       <c r="F316">
         <v>6.282245011565E12</v>
       </c>
-      <c r="G316" s="5" t="s">
+      <c r="G316" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J316" t="s">
@@ -19393,7 +19392,7 @@
       <c r="F317">
         <v>6.282398496261E12</v>
       </c>
-      <c r="G317" s="5" t="s">
+      <c r="G317" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="J317" t="s">
@@ -19690,13 +19689,16 @@
         <v>1488</v>
       </c>
       <c r="J327" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K327">
-        <v>0.0</v>
+        <v>1.0</v>
+      </c>
+      <c r="L327" t="s">
+        <v>1489</v>
       </c>
       <c r="M327" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -19704,19 +19706,19 @@
         <v>327.0</v>
       </c>
       <c r="B328" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="C328" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="D328" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="F328">
         <v>6.28225027397E12</v>
       </c>
       <c r="G328" s="4" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="J328" t="s">
         <v>16</v>
@@ -19725,7 +19727,7 @@
         <v>1.0</v>
       </c>
       <c r="M328" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -19733,19 +19735,19 @@
         <v>328.0</v>
       </c>
       <c r="B329" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="C329" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="D329" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="F329">
         <v>6.281330219987E12</v>
       </c>
       <c r="G329" s="4" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="J329" t="s">
         <v>16</v>
@@ -19754,7 +19756,7 @@
         <v>1.0</v>
       </c>
       <c r="M329" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="330" ht="14.25" customHeight="1">
@@ -19762,19 +19764,19 @@
         <v>329.0</v>
       </c>
       <c r="B330" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="C330" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="D330" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="F330">
         <v>6.282158657003E12</v>
       </c>
       <c r="G330" s="4" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="J330" t="s">
         <v>16</v>
@@ -19783,7 +19785,7 @@
         <v>1.0</v>
       </c>
       <c r="M330" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -19791,19 +19793,19 @@
         <v>330.0</v>
       </c>
       <c r="B331" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="C331" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="D331" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="F331">
         <v>6.282111274698E12</v>
       </c>
       <c r="G331" s="4" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="J331" t="s">
         <v>16</v>
@@ -19812,7 +19814,7 @@
         <v>1.0</v>
       </c>
       <c r="M331" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -19820,19 +19822,19 @@
         <v>331.0</v>
       </c>
       <c r="B332" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="C332" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="D332" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="F332">
         <v>6.28965377047E12</v>
       </c>
       <c r="G332" s="4" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="J332" t="s">
         <v>16</v>
@@ -19841,7 +19843,7 @@
         <v>1.0</v>
       </c>
       <c r="M332" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -19849,19 +19851,19 @@
         <v>332.0</v>
       </c>
       <c r="B333" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="C333" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="D333" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="F333">
         <v>6.281515070883E12</v>
       </c>
       <c r="G333" s="4" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="J333" t="s">
         <v>16</v>
@@ -19870,7 +19872,7 @@
         <v>1.0</v>
       </c>
       <c r="M333" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -19878,19 +19880,19 @@
         <v>333.0</v>
       </c>
       <c r="B334" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="C334" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="D334" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="F334">
         <v>6.282232489901E12</v>
       </c>
       <c r="G334" s="4" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="J334" t="s">
         <v>16</v>
@@ -19899,7 +19901,7 @@
         <v>1.0</v>
       </c>
       <c r="M334" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="335" ht="14.25" customHeight="1">
@@ -19907,19 +19909,19 @@
         <v>334.0</v>
       </c>
       <c r="B335" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="C335" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="D335" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="F335">
         <v>6.289541354675E13</v>
       </c>
       <c r="G335" s="4" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="J335" t="s">
         <v>16</v>
@@ -19928,7 +19930,7 @@
         <v>1.0</v>
       </c>
       <c r="M335" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -19936,19 +19938,19 @@
         <v>335.0</v>
       </c>
       <c r="B336" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="C336" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="D336" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="F336">
         <v>6.281380396763E12</v>
       </c>
       <c r="G336" s="4" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="J336" t="s">
         <v>16</v>
@@ -19957,7 +19959,7 @@
         <v>1.0</v>
       </c>
       <c r="M336" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -19965,19 +19967,19 @@
         <v>336.0</v>
       </c>
       <c r="B337" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="C337" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="D337" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="F337">
         <v>6.285349564445E12</v>
       </c>
       <c r="G337" s="4" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="J337" t="s">
         <v>16</v>
@@ -19986,7 +19988,7 @@
         <v>1.0</v>
       </c>
       <c r="M337" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -19994,19 +19996,19 @@
         <v>337.0</v>
       </c>
       <c r="B338" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="C338" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="D338" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="F338">
         <v>6.281248338907E12</v>
       </c>
       <c r="G338" s="4" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="J338" t="s">
         <v>26</v>
@@ -20015,7 +20017,7 @@
         <v>0.0</v>
       </c>
       <c r="M338" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -20023,19 +20025,19 @@
         <v>338.0</v>
       </c>
       <c r="B339" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="C339" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="D339" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="F339">
         <v>6.281248572503E12</v>
       </c>
       <c r="G339" s="4" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="J339" t="s">
         <v>16</v>
@@ -20044,7 +20046,7 @@
         <v>1.0</v>
       </c>
       <c r="M339" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="340" ht="14.25" customHeight="1">
@@ -20052,19 +20054,19 @@
         <v>339.0</v>
       </c>
       <c r="B340" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="C340" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="D340" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="F340">
         <v>6.282132118988E12</v>
       </c>
       <c r="G340" s="4" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="J340" t="s">
         <v>26</v>
@@ -20073,7 +20075,7 @@
         <v>0.0</v>
       </c>
       <c r="M340" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -20081,19 +20083,19 @@
         <v>340.0</v>
       </c>
       <c r="B341" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="C341" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="D341" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="F341">
         <v>6.281217756961E12</v>
       </c>
       <c r="G341" s="4" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="J341" t="s">
         <v>16</v>
@@ -20102,7 +20104,7 @@
         <v>1.0</v>
       </c>
       <c r="M341" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -20110,19 +20112,19 @@
         <v>341.0</v>
       </c>
       <c r="B342" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="C342" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="D342" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="F342">
         <v>6.281310703971E12</v>
       </c>
       <c r="G342" s="4" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="J342" t="s">
         <v>16</v>
@@ -20131,7 +20133,7 @@
         <v>1.0</v>
       </c>
       <c r="M342" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -20139,19 +20141,19 @@
         <v>342.0</v>
       </c>
       <c r="B343" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="C343" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="D343" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="F343">
         <v>6.281359157737E12</v>
       </c>
       <c r="G343" s="4" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="J343" t="s">
         <v>16</v>
@@ -20160,7 +20162,7 @@
         <v>1.0</v>
       </c>
       <c r="M343" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -20168,19 +20170,19 @@
         <v>343.0</v>
       </c>
       <c r="B344" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="C344" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="D344" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="F344">
         <v>6.285746769578E12</v>
       </c>
       <c r="G344" s="4" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="J344" t="s">
         <v>16</v>
@@ -20189,7 +20191,7 @@
         <v>1.0</v>
       </c>
       <c r="M344" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="345" ht="14.25" customHeight="1">
@@ -20197,19 +20199,19 @@
         <v>344.0</v>
       </c>
       <c r="B345" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="C345" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="D345" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="F345">
         <v>6.282236818409E12</v>
       </c>
       <c r="G345" s="4" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="J345" t="s">
         <v>16</v>
@@ -20218,7 +20220,7 @@
         <v>1.0</v>
       </c>
       <c r="M345" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -20226,19 +20228,19 @@
         <v>345.0</v>
       </c>
       <c r="B346" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="C346" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="D346" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="F346">
         <v>6.282245450138E12</v>
       </c>
       <c r="G346" s="4" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="J346" t="s">
         <v>26</v>
@@ -20247,7 +20249,7 @@
         <v>0.0</v>
       </c>
       <c r="M346" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -20255,19 +20257,19 @@
         <v>346.0</v>
       </c>
       <c r="B347" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="C347" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="D347" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="F347">
         <v>6.2895385387111E13</v>
       </c>
       <c r="G347" s="4" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="J347" t="s">
         <v>16</v>
@@ -20276,7 +20278,7 @@
         <v>1.0</v>
       </c>
       <c r="M347" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -20284,19 +20286,19 @@
         <v>347.0</v>
       </c>
       <c r="B348" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="C348" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="D348" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="F348">
         <v>6.28219415005E12</v>
       </c>
       <c r="G348" s="4" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="J348" t="s">
         <v>16</v>
@@ -20305,7 +20307,7 @@
         <v>1.0</v>
       </c>
       <c r="M348" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -20313,19 +20315,19 @@
         <v>348.0</v>
       </c>
       <c r="B349" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="C349" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="D349" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="F349">
         <v>6.28133624729E12</v>
       </c>
       <c r="G349" s="4" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="J349" t="s">
         <v>16</v>
@@ -20334,7 +20336,7 @@
         <v>1.0</v>
       </c>
       <c r="M349" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="350" ht="14.25" customHeight="1">
@@ -20342,19 +20344,19 @@
         <v>349.0</v>
       </c>
       <c r="B350" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="C350" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="D350" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="F350">
         <v>6.28113822112E11</v>
       </c>
       <c r="G350" s="4" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="J350" t="s">
         <v>16</v>
@@ -20363,7 +20365,7 @@
         <v>1.0</v>
       </c>
       <c r="M350" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -20371,19 +20373,19 @@
         <v>350.0</v>
       </c>
       <c r="B351" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="C351" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="D351" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="F351">
         <v>6.281999259938E12</v>
       </c>
       <c r="G351" s="4" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="J351" t="s">
         <v>16</v>
@@ -20392,7 +20394,7 @@
         <v>1.0</v>
       </c>
       <c r="M351" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -20400,19 +20402,19 @@
         <v>351.0</v>
       </c>
       <c r="B352" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="C352" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="D352" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="F352">
         <v>6.281269713322E12</v>
       </c>
       <c r="G352" s="4" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="J352" t="s">
         <v>16</v>
@@ -20421,7 +20423,7 @@
         <v>1.0</v>
       </c>
       <c r="M352" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -20429,19 +20431,19 @@
         <v>352.0</v>
       </c>
       <c r="B353" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="C353" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="D353" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="F353">
         <v>6.2812420889E12</v>
       </c>
       <c r="G353" s="4" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="J353" t="s">
         <v>16</v>
@@ -20450,7 +20452,7 @@
         <v>1.0</v>
       </c>
       <c r="M353" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -20458,19 +20460,19 @@
         <v>353.0</v>
       </c>
       <c r="B354" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="C354" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="D354" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="F354">
         <v>6.281216072662E12</v>
       </c>
       <c r="G354" s="4" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="J354" t="s">
         <v>16</v>
@@ -20479,7 +20481,7 @@
         <v>1.0</v>
       </c>
       <c r="M354" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="355" ht="14.25" customHeight="1">
@@ -20487,19 +20489,19 @@
         <v>354.0</v>
       </c>
       <c r="B355" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="C355" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="D355" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="F355">
         <v>6.281231634382E12</v>
       </c>
       <c r="G355" s="4" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="J355" t="s">
         <v>16</v>
@@ -20508,10 +20510,10 @@
         <v>1.0</v>
       </c>
       <c r="L355" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="M355" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -20519,19 +20521,19 @@
         <v>355.0</v>
       </c>
       <c r="B356" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="C356" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="D356" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="F356">
         <v>6.285385392002E12</v>
       </c>
       <c r="G356" s="4" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="J356" t="s">
         <v>16</v>
@@ -20540,7 +20542,7 @@
         <v>1.0</v>
       </c>
       <c r="M356" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -20548,19 +20550,19 @@
         <v>356.0</v>
       </c>
       <c r="B357" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="C357" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="D357" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="F357">
         <v>6.2898697726E11</v>
       </c>
       <c r="G357" s="4" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="J357" t="s">
         <v>16</v>
@@ -20569,7 +20571,7 @@
         <v>1.0</v>
       </c>
       <c r="M357" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -20577,19 +20579,19 @@
         <v>357.0</v>
       </c>
       <c r="B358" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="C358" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="D358" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="F358">
         <v>6.287899115808E12</v>
       </c>
       <c r="G358" s="4" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="J358" t="s">
         <v>26</v>
@@ -20598,7 +20600,7 @@
         <v>0.0</v>
       </c>
       <c r="M358" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -20606,19 +20608,19 @@
         <v>358.0</v>
       </c>
       <c r="B359" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="C359" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="D359" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="F359">
         <v>6.282228053857E12</v>
       </c>
       <c r="G359" s="4" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="J359" t="s">
         <v>16</v>
@@ -20627,7 +20629,7 @@
         <v>1.0</v>
       </c>
       <c r="M359" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="360" ht="14.25" customHeight="1">
@@ -20635,19 +20637,19 @@
         <v>359.0</v>
       </c>
       <c r="B360" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="C360" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="D360" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="F360">
         <v>6.28533490869E12</v>
       </c>
       <c r="G360" s="4" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="J360" t="s">
         <v>16</v>
@@ -20656,7 +20658,7 @@
         <v>1.0</v>
       </c>
       <c r="M360" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -20664,19 +20666,19 @@
         <v>360.0</v>
       </c>
       <c r="B361" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="C361" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="D361" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="F361">
         <v>6.282191608887E12</v>
       </c>
       <c r="G361" s="4" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="J361" t="s">
         <v>16</v>
@@ -20685,7 +20687,7 @@
         <v>1.0</v>
       </c>
       <c r="M361" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -20693,19 +20695,19 @@
         <v>361.0</v>
       </c>
       <c r="B362" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="C362" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="D362" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="F362">
         <v>6.289531857601E12</v>
       </c>
       <c r="G362" s="4" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="J362" t="s">
         <v>16</v>
@@ -20714,7 +20716,7 @@
         <v>1.0</v>
       </c>
       <c r="M362" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -20722,19 +20724,19 @@
         <v>362.0</v>
       </c>
       <c r="B363" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="C363" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="D363" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="F363">
         <v>6.281239082153E12</v>
       </c>
       <c r="G363" s="4" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="J363" t="s">
         <v>16</v>
@@ -20743,7 +20745,7 @@
         <v>1.0</v>
       </c>
       <c r="M363" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -20751,19 +20753,19 @@
         <v>363.0</v>
       </c>
       <c r="B364" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="C364" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="D364" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="F364">
         <v>6.282325775656E12</v>
       </c>
       <c r="G364" s="4" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="J364" t="s">
         <v>107</v>
@@ -20772,7 +20774,7 @@
         <v>0.0</v>
       </c>
       <c r="M364" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="365" ht="14.25" customHeight="1">
@@ -20780,19 +20782,19 @@
         <v>364.0</v>
       </c>
       <c r="B365" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="C365" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="D365" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="F365" t="s">
         <v>295</v>
       </c>
       <c r="G365" s="4" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="J365" t="s">
         <v>26</v>
@@ -20801,7 +20803,7 @@
         <v>0.0</v>
       </c>
       <c r="M365" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -20809,19 +20811,19 @@
         <v>365.0</v>
       </c>
       <c r="B366" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="C366" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="D366" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="F366">
         <v>6.282165951254E12</v>
       </c>
       <c r="G366" s="4" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="J366" t="s">
         <v>16</v>
@@ -20830,7 +20832,7 @@
         <v>1.0</v>
       </c>
       <c r="M366" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -20838,19 +20840,19 @@
         <v>366.0</v>
       </c>
       <c r="B367" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="C367" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="D367" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="F367">
         <v>6.282194551568E12</v>
       </c>
       <c r="G367" s="4" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="J367" t="s">
         <v>16</v>
@@ -20859,7 +20861,7 @@
         <v>1.0</v>
       </c>
       <c r="M367" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -20867,19 +20869,19 @@
         <v>367.0</v>
       </c>
       <c r="B368" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="C368" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="D368" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="F368">
         <v>6.285753094405E12</v>
       </c>
       <c r="G368" s="4" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="J368" t="s">
         <v>26</v>
@@ -20888,7 +20890,7 @@
         <v>0.0</v>
       </c>
       <c r="M368" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -20896,19 +20898,19 @@
         <v>368.0</v>
       </c>
       <c r="B369" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="C369" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="D369" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="F369">
         <v>6.281276109334E12</v>
       </c>
       <c r="G369" s="4" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="J369" t="s">
         <v>16</v>
@@ -20917,7 +20919,7 @@
         <v>1.0</v>
       </c>
       <c r="M369" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="370" ht="14.25" customHeight="1">
@@ -20925,19 +20927,19 @@
         <v>369.0</v>
       </c>
       <c r="B370" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="C370" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="D370" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="F370">
         <v>6.285336554817E12</v>
       </c>
       <c r="G370" s="4" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="J370" t="s">
         <v>16</v>
@@ -20946,7 +20948,7 @@
         <v>1.0</v>
       </c>
       <c r="M370" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -20954,19 +20956,19 @@
         <v>370.0</v>
       </c>
       <c r="B371" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="C371" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="D371" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="F371">
         <v>6.285755797096E12</v>
       </c>
       <c r="G371" s="4" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="J371" t="s">
         <v>16</v>
@@ -20975,7 +20977,7 @@
         <v>1.0</v>
       </c>
       <c r="M371" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -20983,19 +20985,19 @@
         <v>371.0</v>
       </c>
       <c r="B372" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="C372" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="D372" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="F372">
         <v>6.28775551795E12</v>
       </c>
       <c r="G372" s="4" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="J372" t="s">
         <v>16</v>
@@ -21004,7 +21006,7 @@
         <v>1.0</v>
       </c>
       <c r="M372" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -21012,19 +21014,19 @@
         <v>372.0</v>
       </c>
       <c r="B373" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="C373" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="D373" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="F373">
         <v>6.281259337261E12</v>
       </c>
       <c r="G373" s="4" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="J373" t="s">
         <v>16</v>
@@ -21033,7 +21035,7 @@
         <v>1.0</v>
       </c>
       <c r="M373" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -21041,28 +21043,31 @@
         <v>373.0</v>
       </c>
       <c r="B374" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="C374" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="D374" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="F374">
         <v>6.281930183888E12</v>
       </c>
       <c r="G374" s="4" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="J374" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K374">
-        <v>0.0</v>
+        <v>1.0</v>
+      </c>
+      <c r="L374" t="s">
+        <v>1726</v>
       </c>
       <c r="M374" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="375" ht="14.25" customHeight="1">
@@ -21070,19 +21075,19 @@
         <v>374.0</v>
       </c>
       <c r="B375" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="C375" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="D375" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
       <c r="F375">
         <v>6.28981305574E11</v>
       </c>
       <c r="G375" s="4" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="J375" t="s">
         <v>16</v>
@@ -21091,7 +21096,7 @@
         <v>1.0</v>
       </c>
       <c r="M375" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -21099,19 +21104,19 @@
         <v>375.0</v>
       </c>
       <c r="B376" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="C376" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="D376" t="s">
-        <v>1733</v>
+        <v>1735</v>
       </c>
       <c r="F376">
         <v>6.281333619346E12</v>
       </c>
       <c r="G376" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="J376" t="s">
         <v>16</v>
@@ -21120,7 +21125,7 @@
         <v>1.0</v>
       </c>
       <c r="M376" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -21128,19 +21133,19 @@
         <v>376.0</v>
       </c>
       <c r="B377" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="C377" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="D377" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="F377">
         <v>6.282131586725E12</v>
       </c>
       <c r="G377" s="4" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="J377" t="s">
         <v>16</v>
@@ -21149,7 +21154,7 @@
         <v>1.0</v>
       </c>
       <c r="M377" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -21157,19 +21162,19 @@
         <v>377.0</v>
       </c>
       <c r="B378" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="C378" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="D378" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="F378">
         <v>6.282143433389E12</v>
       </c>
       <c r="G378" s="4" t="s">
-        <v>1744</v>
+        <v>1746</v>
       </c>
       <c r="J378" t="s">
         <v>16</v>
@@ -21178,7 +21183,7 @@
         <v>1.0</v>
       </c>
       <c r="M378" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -21186,19 +21191,19 @@
         <v>378.0</v>
       </c>
       <c r="B379" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="C379" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="D379" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
       <c r="F379">
         <v>6.281221410897E12</v>
       </c>
       <c r="G379" s="4" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
       <c r="J379" t="s">
         <v>16</v>
@@ -21207,7 +21212,7 @@
         <v>1.0</v>
       </c>
       <c r="M379" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="380" ht="14.25" customHeight="1">
@@ -21215,19 +21220,19 @@
         <v>379.0</v>
       </c>
       <c r="B380" t="s">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="C380" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="D380" t="s">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="F380">
         <v>6.2821465582E12</v>
       </c>
       <c r="G380" s="4" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="J380" t="s">
         <v>16</v>
@@ -21236,10 +21241,10 @@
         <v>1.0</v>
       </c>
       <c r="L380" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
       <c r="M380" t="s">
-        <v>1756</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -21247,19 +21252,19 @@
         <v>380.0</v>
       </c>
       <c r="B381" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="C381" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
       <c r="D381" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
       <c r="F381">
         <v>6.282142860849E12</v>
       </c>
       <c r="G381" s="4" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="J381" t="s">
         <v>16</v>
@@ -21268,7 +21273,7 @@
         <v>1.0</v>
       </c>
       <c r="M381" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -21276,19 +21281,19 @@
         <v>381.0</v>
       </c>
       <c r="B382" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="C382" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="D382" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="F382">
         <v>6.282353079596E12</v>
       </c>
       <c r="G382" s="4" t="s">
-        <v>1765</v>
+        <v>1767</v>
       </c>
       <c r="J382" t="s">
         <v>16</v>
@@ -21297,7 +21302,7 @@
         <v>1.0</v>
       </c>
       <c r="M382" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -21305,19 +21310,19 @@
         <v>382.0</v>
       </c>
       <c r="B383" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="C383" t="s">
-        <v>1768</v>
+        <v>1770</v>
       </c>
       <c r="D383" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="F383">
         <v>6.285231869589E12</v>
       </c>
       <c r="G383" s="4" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
       <c r="J383" t="s">
         <v>16</v>
@@ -21326,7 +21331,7 @@
         <v>1.0</v>
       </c>
       <c r="M383" t="s">
-        <v>1771</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -21334,19 +21339,19 @@
         <v>383.0</v>
       </c>
       <c r="B384" t="s">
-        <v>1772</v>
+        <v>1774</v>
       </c>
       <c r="C384" t="s">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="D384" t="s">
-        <v>1774</v>
+        <v>1776</v>
       </c>
       <c r="F384">
         <v>6.28214213495E12</v>
       </c>
       <c r="G384" s="4" t="s">
-        <v>1775</v>
+        <v>1777</v>
       </c>
       <c r="J384" t="s">
         <v>16</v>
@@ -21355,7 +21360,7 @@
         <v>1.0</v>
       </c>
       <c r="M384" t="s">
-        <v>1776</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="385" ht="14.25" customHeight="1">
@@ -21363,19 +21368,19 @@
         <v>384.0</v>
       </c>
       <c r="B385" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="C385" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="D385" t="s">
-        <v>1779</v>
+        <v>1781</v>
       </c>
       <c r="F385">
         <v>6.28124628325E12</v>
       </c>
       <c r="G385" s="4" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
       <c r="J385" t="s">
         <v>16</v>
@@ -21384,7 +21389,7 @@
         <v>1.0</v>
       </c>
       <c r="M385" t="s">
-        <v>1781</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -21392,19 +21397,19 @@
         <v>385.0</v>
       </c>
       <c r="B386" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="C386" t="s">
-        <v>1783</v>
+        <v>1785</v>
       </c>
       <c r="D386" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="F386">
         <v>6.289668302258E12</v>
       </c>
       <c r="G386" s="4" t="s">
-        <v>1785</v>
+        <v>1787</v>
       </c>
       <c r="J386" t="s">
         <v>16</v>
@@ -21413,7 +21418,7 @@
         <v>1.0</v>
       </c>
       <c r="M386" t="s">
-        <v>1786</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -21421,19 +21426,19 @@
         <v>386.0</v>
       </c>
       <c r="B387" t="s">
-        <v>1787</v>
+        <v>1789</v>
       </c>
       <c r="C387" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="D387" t="s">
-        <v>1789</v>
+        <v>1791</v>
       </c>
       <c r="F387">
         <v>6.281343257229E12</v>
       </c>
       <c r="G387" s="4" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="J387" t="s">
         <v>16</v>
@@ -21442,7 +21447,7 @@
         <v>1.0</v>
       </c>
       <c r="M387" t="s">
-        <v>1791</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -21450,19 +21455,19 @@
         <v>387.0</v>
       </c>
       <c r="B388" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="C388" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="D388" t="s">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="F388">
         <v>6.281247317199E12</v>
       </c>
       <c r="G388" s="4" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="J388" t="s">
         <v>16</v>
@@ -21471,7 +21476,7 @@
         <v>1.0</v>
       </c>
       <c r="M388" t="s">
-        <v>1796</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -21479,19 +21484,19 @@
         <v>388.0</v>
       </c>
       <c r="B389" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="C389" t="s">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="D389" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="F389">
         <v>6.282143877921E12</v>
       </c>
       <c r="G389" s="4" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="J389" t="s">
         <v>16</v>
@@ -21500,7 +21505,7 @@
         <v>1.0</v>
       </c>
       <c r="M389" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="390" ht="14.25" customHeight="1">
@@ -21508,19 +21513,19 @@
         <v>389.0</v>
       </c>
       <c r="B390" t="s">
-        <v>1802</v>
+        <v>1804</v>
       </c>
       <c r="C390" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="D390" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="F390">
         <v>6.282335288382E12</v>
       </c>
       <c r="G390" s="4" t="s">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="J390" t="s">
         <v>16</v>
@@ -21529,7 +21534,7 @@
         <v>1.0</v>
       </c>
       <c r="M390" t="s">
-        <v>1806</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -21537,19 +21542,19 @@
         <v>390.0</v>
       </c>
       <c r="B391" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="C391" t="s">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="D391" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="F391">
         <v>6.282115070834E12</v>
       </c>
       <c r="G391" s="4" t="s">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="J391" t="s">
         <v>16</v>
@@ -21558,7 +21563,7 @@
         <v>1.0</v>
       </c>
       <c r="M391" t="s">
-        <v>1811</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -21566,19 +21571,19 @@
         <v>391.0</v>
       </c>
       <c r="B392" t="s">
-        <v>1812</v>
+        <v>1814</v>
       </c>
       <c r="C392" t="s">
-        <v>1813</v>
+        <v>1815</v>
       </c>
       <c r="D392" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="F392">
         <v>6.282131985368E12</v>
       </c>
       <c r="G392" s="4" t="s">
-        <v>1815</v>
+        <v>1817</v>
       </c>
       <c r="J392" t="s">
         <v>16</v>
@@ -21587,7 +21592,7 @@
         <v>1.0</v>
       </c>
       <c r="M392" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -21595,19 +21600,19 @@
         <v>392.0</v>
       </c>
       <c r="B393" t="s">
-        <v>1817</v>
+        <v>1819</v>
       </c>
       <c r="C393" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="D393" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="F393">
         <v>6.281211992225E12</v>
       </c>
       <c r="G393" s="4" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="J393" t="s">
         <v>16</v>
@@ -21616,7 +21621,7 @@
         <v>1.0</v>
       </c>
       <c r="M393" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -21624,19 +21629,19 @@
         <v>393.0</v>
       </c>
       <c r="B394" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="C394" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="D394" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="F394">
         <v>6.281231144777E12</v>
       </c>
       <c r="G394" s="4" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="J394" t="s">
         <v>16</v>
@@ -21645,7 +21650,7 @@
         <v>1.0</v>
       </c>
       <c r="M394" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="395" ht="14.25" customHeight="1">
@@ -21653,19 +21658,19 @@
         <v>394.0</v>
       </c>
       <c r="B395" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="C395" t="s">
-        <v>1828</v>
+        <v>1830</v>
       </c>
       <c r="D395" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="F395">
         <v>6.281334327658E12</v>
       </c>
       <c r="G395" s="4" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="J395" t="s">
         <v>16</v>
@@ -21674,7 +21679,7 @@
         <v>1.0</v>
       </c>
       <c r="M395" t="s">
-        <v>1831</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -21682,19 +21687,19 @@
         <v>395.0</v>
       </c>
       <c r="B396" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="C396" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="D396" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="F396">
         <v>6.287763143316E12</v>
       </c>
       <c r="G396" s="4" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="J396" t="s">
         <v>16</v>
@@ -21703,7 +21708,7 @@
         <v>1.0</v>
       </c>
       <c r="M396" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -21711,19 +21716,19 @@
         <v>396.0</v>
       </c>
       <c r="B397" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="C397" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="D397" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="F397">
         <v>6.28995380695E11</v>
       </c>
       <c r="G397" s="4" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="J397" t="s">
         <v>16</v>
@@ -21732,7 +21737,7 @@
         <v>1.0</v>
       </c>
       <c r="M397" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -21740,19 +21745,19 @@
         <v>397.0</v>
       </c>
       <c r="B398" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="C398" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="D398" t="s">
-        <v>1844</v>
+        <v>1846</v>
       </c>
       <c r="F398">
         <v>6.281239095927E12</v>
       </c>
       <c r="G398" s="4" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="J398" t="s">
         <v>16</v>
@@ -21761,7 +21766,7 @@
         <v>1.0</v>
       </c>
       <c r="M398" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -21769,19 +21774,19 @@
         <v>398.0</v>
       </c>
       <c r="B399" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="C399" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="D399" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="F399">
         <v>6.282132108259E12</v>
       </c>
       <c r="G399" s="4" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
       <c r="J399" t="s">
         <v>16</v>
@@ -21790,7 +21795,7 @@
         <v>1.0</v>
       </c>
       <c r="M399" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="400" ht="14.25" customHeight="1">
@@ -21798,28 +21803,28 @@
         <v>399.0</v>
       </c>
       <c r="B400" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="C400" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="D400" t="s">
-        <v>1854</v>
+        <v>1856</v>
       </c>
       <c r="F400">
         <v>6.285823316926E12</v>
       </c>
       <c r="G400" s="4" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="J400" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K400">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M400" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -21827,19 +21832,19 @@
         <v>400.0</v>
       </c>
       <c r="B401" t="s">
-        <v>1857</v>
+        <v>1859</v>
       </c>
       <c r="C401" t="s">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="D401" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="F401">
         <v>6.287777939158E12</v>
       </c>
       <c r="G401" s="4" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
       <c r="J401" t="s">
         <v>16</v>
@@ -21848,7 +21853,7 @@
         <v>1.0</v>
       </c>
       <c r="M401" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -21856,19 +21861,19 @@
         <v>401.0</v>
       </c>
       <c r="B402" t="s">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="C402" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="D402" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="F402">
         <v>6.285100263333E12</v>
       </c>
       <c r="G402" s="4" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="J402" t="s">
         <v>16</v>
@@ -21877,7 +21882,7 @@
         <v>1.0</v>
       </c>
       <c r="M402" t="s">
-        <v>1866</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -21885,19 +21890,19 @@
         <v>402.0</v>
       </c>
       <c r="B403" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="C403" t="s">
-        <v>1868</v>
+        <v>1870</v>
       </c>
       <c r="D403" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="F403">
         <v>6.289686357931E12</v>
       </c>
       <c r="G403" s="4" t="s">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="J403" t="s">
         <v>16</v>
@@ -21906,7 +21911,7 @@
         <v>1.0</v>
       </c>
       <c r="M403" t="s">
-        <v>1871</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -21914,19 +21919,19 @@
         <v>403.0</v>
       </c>
       <c r="B404" t="s">
-        <v>1872</v>
+        <v>1874</v>
       </c>
       <c r="C404" t="s">
-        <v>1873</v>
+        <v>1875</v>
       </c>
       <c r="D404" t="s">
-        <v>1874</v>
+        <v>1876</v>
       </c>
       <c r="F404">
         <v>6.285230740685E12</v>
       </c>
       <c r="G404" s="4" t="s">
-        <v>1875</v>
+        <v>1877</v>
       </c>
       <c r="J404" t="s">
         <v>16</v>
@@ -21935,7 +21940,7 @@
         <v>1.0</v>
       </c>
       <c r="M404" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="405" ht="14.25" customHeight="1">
@@ -21943,19 +21948,19 @@
         <v>404.0</v>
       </c>
       <c r="B405" t="s">
-        <v>1877</v>
+        <v>1879</v>
       </c>
       <c r="C405" t="s">
-        <v>1878</v>
+        <v>1880</v>
       </c>
       <c r="D405" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="F405">
         <v>6.281231454268E12</v>
       </c>
       <c r="G405" s="4" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="J405" t="s">
         <v>26</v>
@@ -21964,7 +21969,7 @@
         <v>0.0</v>
       </c>
       <c r="M405" t="s">
-        <v>1881</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -21972,19 +21977,19 @@
         <v>405.0</v>
       </c>
       <c r="B406" t="s">
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="C406" t="s">
-        <v>1883</v>
+        <v>1885</v>
       </c>
       <c r="D406" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="F406">
         <v>6.281351985766E12</v>
       </c>
       <c r="G406" s="4" t="s">
-        <v>1885</v>
+        <v>1887</v>
       </c>
       <c r="J406" t="s">
         <v>16</v>
@@ -21993,7 +21998,7 @@
         <v>1.0</v>
       </c>
       <c r="M406" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -22001,19 +22006,19 @@
         <v>406.0</v>
       </c>
       <c r="B407" t="s">
-        <v>1887</v>
+        <v>1889</v>
       </c>
       <c r="C407" t="s">
-        <v>1888</v>
+        <v>1890</v>
       </c>
       <c r="D407" t="s">
-        <v>1889</v>
+        <v>1891</v>
       </c>
       <c r="F407">
         <v>6.282230091339E12</v>
       </c>
       <c r="G407" s="4" t="s">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="J407" t="s">
         <v>16</v>
@@ -22022,7 +22027,7 @@
         <v>1.0</v>
       </c>
       <c r="M407" t="s">
-        <v>1891</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -22030,19 +22035,19 @@
         <v>407.0</v>
       </c>
       <c r="B408" t="s">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="C408" t="s">
-        <v>1893</v>
+        <v>1895</v>
       </c>
       <c r="D408" t="s">
-        <v>1894</v>
+        <v>1896</v>
       </c>
       <c r="F408">
         <v>6.285266849963E12</v>
       </c>
       <c r="G408" s="4" t="s">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="J408" t="s">
         <v>16</v>
@@ -22051,7 +22056,7 @@
         <v>1.0</v>
       </c>
       <c r="M408" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -22059,19 +22064,19 @@
         <v>408.0</v>
       </c>
       <c r="B409" t="s">
-        <v>1897</v>
+        <v>1899</v>
       </c>
       <c r="C409" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="D409" t="s">
-        <v>1899</v>
+        <v>1901</v>
       </c>
       <c r="F409">
         <v>6.281357694467E12</v>
       </c>
       <c r="G409" s="4" t="s">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="J409" t="s">
         <v>16</v>
@@ -22080,7 +22085,7 @@
         <v>1.0</v>
       </c>
       <c r="M409" t="s">
-        <v>1901</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="410" ht="14.25" customHeight="1">
@@ -22088,19 +22093,19 @@
         <v>409.0</v>
       </c>
       <c r="B410" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="C410" t="s">
-        <v>1903</v>
+        <v>1905</v>
       </c>
       <c r="D410" t="s">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="F410">
         <v>6.285102747555E12</v>
       </c>
       <c r="G410" s="4" t="s">
-        <v>1905</v>
+        <v>1907</v>
       </c>
       <c r="J410" t="s">
         <v>16</v>
@@ -22109,7 +22114,7 @@
         <v>1.0</v>
       </c>
       <c r="M410" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -22117,19 +22122,19 @@
         <v>410.0</v>
       </c>
       <c r="B411" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="C411" t="s">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="D411" t="s">
-        <v>1909</v>
+        <v>1911</v>
       </c>
       <c r="F411">
         <v>6.2882009058775E13</v>
       </c>
       <c r="G411" s="4" t="s">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="J411" t="s">
         <v>16</v>
@@ -22138,7 +22143,7 @@
         <v>1.0</v>
       </c>
       <c r="M411" t="s">
-        <v>1911</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -22146,19 +22151,19 @@
         <v>411.0</v>
       </c>
       <c r="B412" t="s">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="C412" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="D412" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="F412">
         <v>6.281248449264E12</v>
       </c>
       <c r="G412" s="4" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="J412" t="s">
         <v>16</v>
@@ -22167,7 +22172,7 @@
         <v>1.0</v>
       </c>
       <c r="M412" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -22175,19 +22180,19 @@
         <v>412.0</v>
       </c>
       <c r="B413" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="C413" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="D413" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="F413">
         <v>6.281254656024E12</v>
       </c>
       <c r="G413" s="4" t="s">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="J413" t="s">
         <v>16</v>
@@ -22196,7 +22201,7 @@
         <v>1.0</v>
       </c>
       <c r="M413" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -22204,19 +22209,19 @@
         <v>413.0</v>
       </c>
       <c r="B414" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="C414" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="D414" t="s">
-        <v>1924</v>
+        <v>1926</v>
       </c>
       <c r="F414">
         <v>6.281359239299E12</v>
       </c>
       <c r="G414" s="4" t="s">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="J414" t="s">
         <v>16</v>
@@ -22225,7 +22230,7 @@
         <v>1.0</v>
       </c>
       <c r="M414" t="s">
-        <v>1926</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="415" ht="14.25" customHeight="1">
@@ -22233,19 +22238,19 @@
         <v>414.0</v>
       </c>
       <c r="B415" t="s">
-        <v>1927</v>
+        <v>1929</v>
       </c>
       <c r="C415" t="s">
-        <v>1928</v>
+        <v>1930</v>
       </c>
       <c r="D415" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="F415">
         <v>6.28784469059E12</v>
       </c>
       <c r="G415" s="4" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="J415" t="s">
         <v>16</v>
@@ -22254,7 +22259,7 @@
         <v>1.0</v>
       </c>
       <c r="M415" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -22262,19 +22267,19 @@
         <v>415.0</v>
       </c>
       <c r="B416" t="s">
-        <v>1932</v>
+        <v>1934</v>
       </c>
       <c r="C416" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="D416" t="s">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="F416">
         <v>6.28883305295E11</v>
       </c>
       <c r="G416" s="4" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="J416" t="s">
         <v>16</v>
@@ -22283,7 +22288,7 @@
         <v>1.0</v>
       </c>
       <c r="M416" t="s">
-        <v>1936</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -22291,19 +22296,19 @@
         <v>416.0</v>
       </c>
       <c r="B417" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="C417" t="s">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="D417" t="s">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="F417">
         <v>6.281256979795E12</v>
       </c>
       <c r="G417" s="4" t="s">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="J417" t="s">
         <v>16</v>
@@ -22312,7 +22317,7 @@
         <v>1.0</v>
       </c>
       <c r="M417" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
@@ -22320,19 +22325,19 @@
         <v>417.0</v>
       </c>
       <c r="B418" t="s">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="C418" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="D418" t="s">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="F418">
         <v>6.282154344053E12</v>
       </c>
       <c r="G418" s="4" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="J418" t="s">
         <v>16</v>
@@ -22341,7 +22346,7 @@
         <v>1.0</v>
       </c>
       <c r="M418" t="s">
-        <v>1946</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -22349,19 +22354,19 @@
         <v>418.0</v>
       </c>
       <c r="B419" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="C419" t="s">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="D419" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="F419">
         <v>6.282143731677E12</v>
       </c>
       <c r="G419" s="4" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="J419" t="s">
         <v>16</v>
@@ -22370,7 +22375,7 @@
         <v>1.0</v>
       </c>
       <c r="M419" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="420" ht="14.25" customHeight="1">
@@ -22378,19 +22383,19 @@
         <v>419.0</v>
       </c>
       <c r="B420" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="C420" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="D420" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="F420">
         <v>6.282279365816E12</v>
       </c>
       <c r="G420" s="4" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="J420" t="s">
         <v>16</v>
@@ -22399,7 +22404,7 @@
         <v>1.0</v>
       </c>
       <c r="M420" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -22407,19 +22412,19 @@
         <v>420.0</v>
       </c>
       <c r="B421" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="C421" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="D421" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="F421">
         <v>6.281380310808E12</v>
       </c>
       <c r="G421" s="4" t="s">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="J421" t="s">
         <v>16</v>
@@ -22428,7 +22433,7 @@
         <v>1.0</v>
       </c>
       <c r="M421" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -22436,19 +22441,19 @@
         <v>421.0</v>
       </c>
       <c r="B422" t="s">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="C422" t="s">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="D422" t="s">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="F422">
         <v>6.281235186525E12</v>
       </c>
       <c r="G422" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="J422" t="s">
         <v>16</v>
@@ -22457,7 +22462,7 @@
         <v>1.0</v>
       </c>
       <c r="M422" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
@@ -22465,19 +22470,19 @@
         <v>422.0</v>
       </c>
       <c r="B423" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="C423" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="D423" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="F423">
         <v>6.289561113005E13</v>
       </c>
       <c r="G423" s="4" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="J423" t="s">
         <v>16</v>
@@ -22486,7 +22491,7 @@
         <v>1.0</v>
       </c>
       <c r="M423" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -22494,28 +22499,28 @@
         <v>423.0</v>
       </c>
       <c r="B424" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="C424" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="D424" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="F424">
         <v>6.288989848698E12</v>
       </c>
       <c r="G424" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="J424" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K424">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M424" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="425" ht="14.25" customHeight="1">
@@ -22523,19 +22528,19 @@
         <v>424.0</v>
       </c>
       <c r="B425" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="C425" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="D425" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="F425">
         <v>6.282235104744E12</v>
       </c>
       <c r="G425" s="4" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="J425" t="s">
         <v>16</v>
@@ -22544,7 +22549,7 @@
         <v>1.0</v>
       </c>
       <c r="M425" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -22552,19 +22557,19 @@
         <v>425.0</v>
       </c>
       <c r="B426" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="C426" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="D426" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="F426">
         <v>6.281338607527E12</v>
       </c>
       <c r="G426" s="4" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="J426" t="s">
         <v>16</v>
@@ -22573,7 +22578,7 @@
         <v>1.0</v>
       </c>
       <c r="M426" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -22581,19 +22586,19 @@
         <v>426.0</v>
       </c>
       <c r="B427" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="C427" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="D427" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="F427">
         <v>6.281332553993E12</v>
       </c>
       <c r="G427" s="4" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="J427" t="s">
         <v>16</v>
@@ -22602,7 +22607,7 @@
         <v>1.0</v>
       </c>
       <c r="M427" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
@@ -22610,19 +22615,19 @@
         <v>427.0</v>
       </c>
       <c r="B428" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="C428" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="D428" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="F428">
         <v>6.281257278183E12</v>
       </c>
       <c r="G428" s="4" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="J428" t="s">
         <v>16</v>
@@ -22631,7 +22636,7 @@
         <v>1.0</v>
       </c>
       <c r="M428" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
@@ -22639,19 +22644,19 @@
         <v>428.0</v>
       </c>
       <c r="B429" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="C429" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="D429" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="F429">
         <v>6.285119925867E12</v>
       </c>
       <c r="G429" s="4" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="J429" t="s">
         <v>16</v>
@@ -22660,7 +22665,7 @@
         <v>1.0</v>
       </c>
       <c r="M429" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="430" ht="14.25" customHeight="1">
@@ -22668,19 +22673,19 @@
         <v>429.0</v>
       </c>
       <c r="B430" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="C430" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="D430" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="F430">
         <v>6.285748013203E12</v>
       </c>
       <c r="G430" s="4" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="J430" t="s">
         <v>16</v>
@@ -22689,7 +22694,7 @@
         <v>1.0</v>
       </c>
       <c r="M430" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -22697,19 +22702,19 @@
         <v>430.0</v>
       </c>
       <c r="B431" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="C431" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="D431" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="F431">
         <v>6.282252244664E12</v>
       </c>
       <c r="G431" s="4" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="J431" t="s">
         <v>26</v>
@@ -22718,7 +22723,7 @@
         <v>0.0</v>
       </c>
       <c r="M431" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="432" ht="14.25" customHeight="1">
@@ -22726,19 +22731,19 @@
         <v>431.0</v>
       </c>
       <c r="B432" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C432" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="D432" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="F432">
         <v>6.2812554088E12</v>
       </c>
       <c r="G432" s="4" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="J432" t="s">
         <v>16</v>
@@ -22747,7 +22752,7 @@
         <v>1.0</v>
       </c>
       <c r="M432" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -22755,19 +22760,19 @@
         <v>432.0</v>
       </c>
       <c r="B433" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C433" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D433" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="F433">
         <v>6.282323558935E12</v>
       </c>
       <c r="G433" s="4" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="J433" t="s">
         <v>16</v>
@@ -22776,7 +22781,7 @@
         <v>1.0</v>
       </c>
       <c r="M433" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -22784,19 +22789,19 @@
         <v>433.0</v>
       </c>
       <c r="B434" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C434" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D434" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F434">
         <v>6.281222778764E12</v>
       </c>
       <c r="G434" s="4" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="J434" t="s">
         <v>16</v>
@@ -22805,7 +22810,7 @@
         <v>1.0</v>
       </c>
       <c r="M434" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="435" ht="14.25" customHeight="1">
@@ -22813,19 +22818,19 @@
         <v>434.0</v>
       </c>
       <c r="B435" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="C435" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="D435" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="F435">
         <v>6.281231648005E12</v>
       </c>
       <c r="G435" s="4" t="s">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="J435" t="s">
         <v>16</v>
@@ -22834,10 +22839,10 @@
         <v>1.0</v>
       </c>
       <c r="L435" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="M435" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="436" ht="14.25" customHeight="1">
@@ -22845,19 +22850,19 @@
         <v>435.0</v>
       </c>
       <c r="B436" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="C436" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="D436" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="F436">
         <v>6.28155911182E11</v>
       </c>
       <c r="G436" s="4" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="J436" t="s">
         <v>16</v>
@@ -22866,7 +22871,7 @@
         <v>1.0</v>
       </c>
       <c r="M436" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -22874,19 +22879,19 @@
         <v>436.0</v>
       </c>
       <c r="B437" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="C437" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="D437" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="F437">
         <v>6.28116940108E11</v>
       </c>
       <c r="G437" s="4" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="J437" t="s">
         <v>16</v>
@@ -22895,7 +22900,7 @@
         <v>1.0</v>
       </c>
       <c r="M437" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
@@ -22903,19 +22908,19 @@
         <v>437.0</v>
       </c>
       <c r="B438" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="C438" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="D438" t="s">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="F438">
         <v>6.28114125688E11</v>
       </c>
       <c r="G438" s="4" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="J438" t="s">
         <v>16</v>
@@ -22924,7 +22929,7 @@
         <v>1.0</v>
       </c>
       <c r="M438" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="439" ht="14.25" customHeight="1">
@@ -22932,19 +22937,19 @@
         <v>438.0</v>
       </c>
       <c r="B439" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="C439" t="s">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="D439" t="s">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="F439">
         <v>6.281344647157E12</v>
       </c>
       <c r="G439" s="4" t="s">
-        <v>2051</v>
+        <v>2053</v>
       </c>
       <c r="J439" t="s">
         <v>16</v>
@@ -22953,7 +22958,7 @@
         <v>1.0</v>
       </c>
       <c r="M439" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="440" ht="14.25" customHeight="1">
@@ -22961,19 +22966,19 @@
         <v>439.0</v>
       </c>
       <c r="B440" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="C440" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="D440" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="F440">
         <v>6.282192340064E12</v>
       </c>
       <c r="G440" s="4" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="J440" t="s">
         <v>16</v>
@@ -22982,7 +22987,7 @@
         <v>1.0</v>
       </c>
       <c r="M440" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -22990,19 +22995,19 @@
         <v>440.0</v>
       </c>
       <c r="B441" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="C441" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="D441" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="F441">
         <v>6.285386391234E12</v>
       </c>
       <c r="G441" s="4" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="J441" t="s">
         <v>16</v>
@@ -23011,7 +23016,7 @@
         <v>1.0</v>
       </c>
       <c r="M441" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="442" ht="14.25" customHeight="1">
@@ -23019,19 +23024,19 @@
         <v>441.0</v>
       </c>
       <c r="B442" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="C442" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="D442" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="F442">
         <v>6.287759888288E12</v>
       </c>
       <c r="G442" s="4" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="J442" t="s">
         <v>16</v>
@@ -23040,7 +23045,7 @@
         <v>1.0</v>
       </c>
       <c r="M442" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="443" ht="14.25" customHeight="1">
@@ -23048,19 +23053,19 @@
         <v>442.0</v>
       </c>
       <c r="B443" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="C443" t="s">
-        <v>2069</v>
+        <v>2071</v>
       </c>
       <c r="D443" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="F443">
         <v>6.282181555049E12</v>
       </c>
       <c r="G443" s="4" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="J443" t="s">
         <v>16</v>
@@ -23069,7 +23074,7 @@
         <v>1.0</v>
       </c>
       <c r="M443" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -23077,19 +23082,19 @@
         <v>443.0</v>
       </c>
       <c r="B444" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="C444" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="D444" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="F444">
         <v>6.288102699503E13</v>
       </c>
       <c r="G444" s="4" t="s">
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="J444" t="s">
         <v>16</v>
@@ -23098,7 +23103,7 @@
         <v>1.0</v>
       </c>
       <c r="M444" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="445" ht="14.25" customHeight="1">
@@ -23106,19 +23111,19 @@
         <v>444.0</v>
       </c>
       <c r="B445" t="s">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="C445" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="D445" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="F445">
         <v>6.28999720777E11</v>
       </c>
       <c r="G445" s="4" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="J445" t="s">
         <v>16</v>
@@ -23127,7 +23132,7 @@
         <v>1.0</v>
       </c>
       <c r="M445" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="446" ht="14.25" customHeight="1">
@@ -23135,19 +23140,19 @@
         <v>445.0</v>
       </c>
       <c r="B446" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="C446" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="D446" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="F446">
         <v>6.282198594142E12</v>
       </c>
       <c r="G446" s="4" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="J446" t="s">
         <v>16</v>
@@ -23156,7 +23161,7 @@
         <v>1.0</v>
       </c>
       <c r="M446" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -23164,19 +23169,19 @@
         <v>446.0</v>
       </c>
       <c r="B447" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="C447" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="D447" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="F447">
         <v>6.281352508446E12</v>
       </c>
       <c r="G447" s="4" t="s">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="J447" t="s">
         <v>16</v>
@@ -23185,7 +23190,7 @@
         <v>1.0</v>
       </c>
       <c r="M447" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -23193,19 +23198,19 @@
         <v>447.0</v>
       </c>
       <c r="B448" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="C448" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="D448" t="s">
-        <v>2095</v>
+        <v>2097</v>
       </c>
       <c r="F448">
         <v>6.285749457597E12</v>
       </c>
       <c r="G448" s="4" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="J448" t="s">
         <v>16</v>
@@ -23214,7 +23219,7 @@
         <v>1.0</v>
       </c>
       <c r="M448" t="s">
-        <v>2097</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="449" ht="14.25" customHeight="1">
@@ -23222,19 +23227,19 @@
         <v>448.0</v>
       </c>
       <c r="B449" t="s">
-        <v>2098</v>
+        <v>2100</v>
       </c>
       <c r="C449" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="D449" t="s">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="F449">
         <v>6.281244059389E12</v>
       </c>
       <c r="G449" s="4" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="J449" t="s">
         <v>16</v>
@@ -23243,7 +23248,7 @@
         <v>1.0</v>
       </c>
       <c r="M449" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="450" ht="14.25" customHeight="1">
@@ -23251,19 +23256,19 @@
         <v>449.0</v>
       </c>
       <c r="B450" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="C450" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="D450" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="F450">
         <v>6.281337380561E12</v>
       </c>
       <c r="G450" s="4" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="J450" t="s">
         <v>16</v>
@@ -23272,7 +23277,7 @@
         <v>1.0</v>
       </c>
       <c r="M450" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="451" ht="14.25" customHeight="1">
@@ -23280,19 +23285,19 @@
         <v>450.0</v>
       </c>
       <c r="B451" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="C451" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="D451" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="F451">
         <v>6.281232597299E12</v>
       </c>
       <c r="G451" s="4" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="J451" t="s">
         <v>16</v>
@@ -23301,7 +23306,7 @@
         <v>1.0</v>
       </c>
       <c r="M451" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="452" ht="14.25" customHeight="1">
@@ -23309,19 +23314,19 @@
         <v>451.0</v>
       </c>
       <c r="B452" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="C452" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="D452" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="F452">
         <v>6.28884976868E11</v>
       </c>
       <c r="G452" s="4" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="J452" t="s">
         <v>16</v>
@@ -23330,7 +23335,7 @@
         <v>1.0</v>
       </c>
       <c r="M452" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="453" ht="14.25" customHeight="1">
@@ -23338,19 +23343,19 @@
         <v>452.0</v>
       </c>
       <c r="B453" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="C453" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="D453" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="F453">
         <v>6.285348530518E12</v>
       </c>
       <c r="G453" s="4" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="J453" t="s">
         <v>26</v>
@@ -23359,7 +23364,7 @@
         <v>0.0</v>
       </c>
       <c r="M453" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="454" ht="14.25" customHeight="1">
@@ -23367,19 +23372,19 @@
         <v>453.0</v>
       </c>
       <c r="B454" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="C454" t="s">
-        <v>2124</v>
+        <v>2126</v>
       </c>
       <c r="D454" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="F454">
         <v>6.281325802533E12</v>
       </c>
       <c r="G454" s="4" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="J454" t="s">
         <v>16</v>
@@ -23388,7 +23393,7 @@
         <v>1.0</v>
       </c>
       <c r="M454" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="455" ht="14.25" customHeight="1">
@@ -23396,19 +23401,19 @@
         <v>454.0</v>
       </c>
       <c r="B455" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="C455" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="D455" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="F455">
         <v>6.281338869875E12</v>
       </c>
       <c r="G455" s="4" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="J455" t="s">
         <v>16</v>
@@ -23417,7 +23422,7 @@
         <v>1.0</v>
       </c>
       <c r="M455" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="456" ht="14.25" customHeight="1">
@@ -23425,19 +23430,19 @@
         <v>455.0</v>
       </c>
       <c r="B456" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="C456" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="D456" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="F456">
         <v>6.2895611993599E13</v>
       </c>
       <c r="G456" s="4" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="J456" t="s">
         <v>16</v>
@@ -23446,7 +23451,7 @@
         <v>1.0</v>
       </c>
       <c r="M456" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="457" ht="14.25" customHeight="1">
@@ -23454,19 +23459,19 @@
         <v>456.0</v>
       </c>
       <c r="B457" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="C457" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="D457" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="F457">
         <v>6.281282669978E12</v>
       </c>
       <c r="G457" s="4" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="J457" t="s">
         <v>16</v>
@@ -23475,7 +23480,7 @@
         <v>1.0</v>
       </c>
       <c r="M457" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="458" ht="14.25" customHeight="1">
@@ -23483,19 +23488,19 @@
         <v>457.0</v>
       </c>
       <c r="B458" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="C458" t="s">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="D458" t="s">
-        <v>2145</v>
+        <v>2147</v>
       </c>
       <c r="F458">
         <v>6.281388885107E12</v>
       </c>
       <c r="G458" s="4" t="s">
-        <v>2146</v>
+        <v>2148</v>
       </c>
       <c r="J458" t="s">
         <v>16</v>
@@ -23504,7 +23509,7 @@
         <v>1.0</v>
       </c>
       <c r="M458" t="s">
-        <v>2147</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="459" ht="14.25" customHeight="1">
@@ -23512,19 +23517,19 @@
         <v>458.0</v>
       </c>
       <c r="B459" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
       <c r="C459" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="D459" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="F459">
         <v>6.285933820798E12</v>
       </c>
       <c r="G459" s="4" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="J459" t="s">
         <v>16</v>
@@ -23533,7 +23538,7 @@
         <v>1.0</v>
       </c>
       <c r="M459" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="460" ht="14.25" customHeight="1">
@@ -23541,19 +23546,19 @@
         <v>459.0</v>
       </c>
       <c r="B460" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
       <c r="C460" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="D460" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
       <c r="F460">
         <v>6.281355105552E12</v>
       </c>
       <c r="G460" s="4" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="J460" t="s">
         <v>16</v>
@@ -23562,7 +23567,7 @@
         <v>1.0</v>
       </c>
       <c r="M460" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="461" ht="14.25" customHeight="1">
@@ -23570,28 +23575,28 @@
         <v>460.0</v>
       </c>
       <c r="B461" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="C461" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="D461" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="F461">
         <v>6.282154959321E12</v>
       </c>
       <c r="G461" s="4" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="J461" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="K461">
         <v>0.0</v>
       </c>
       <c r="M461" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="462" ht="14.25" customHeight="1">
@@ -23599,19 +23604,19 @@
         <v>461.0</v>
       </c>
       <c r="B462" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="C462" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="D462" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="F462">
         <v>6.282119161786E12</v>
       </c>
       <c r="G462" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J462" t="s">
         <v>16</v>
@@ -23620,7 +23625,7 @@
         <v>1.0</v>
       </c>
       <c r="M462" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="463" ht="14.25" customHeight="1">
@@ -23628,19 +23633,19 @@
         <v>462.0</v>
       </c>
       <c r="B463" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="C463" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="D463" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="F463">
         <v>6.281252957374E12</v>
       </c>
       <c r="G463" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="J463" t="s">
         <v>16</v>
@@ -23649,7 +23654,7 @@
         <v>1.0</v>
       </c>
       <c r="M463" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="464" ht="14.25" customHeight="1">
@@ -23657,19 +23662,19 @@
         <v>463.0</v>
       </c>
       <c r="B464" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="C464" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="D464" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="F464">
         <v>6.28314011693E12</v>
       </c>
       <c r="G464" s="4" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="J464" t="s">
         <v>16</v>
@@ -23678,7 +23683,7 @@
         <v>1.0</v>
       </c>
       <c r="M464" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="465" ht="14.25" customHeight="1">
@@ -23686,19 +23691,19 @@
         <v>464.0</v>
       </c>
       <c r="B465" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="C465" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="D465" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="F465">
         <v>6.282282300051E12</v>
       </c>
       <c r="G465" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J465" t="s">
         <v>16</v>
@@ -23707,7 +23712,7 @@
         <v>1.0</v>
       </c>
       <c r="M465" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="466" ht="14.25" customHeight="1">
@@ -23715,19 +23720,19 @@
         <v>465.0</v>
       </c>
       <c r="B466" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="C466" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="D466" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="F466">
         <v>6.281524924437E12</v>
       </c>
       <c r="G466" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="J466" t="s">
         <v>16</v>
@@ -23736,7 +23741,7 @@
         <v>1.0</v>
       </c>
       <c r="M466" t="s">
-        <v>2187</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="467" ht="14.25" customHeight="1">
@@ -23744,19 +23749,19 @@
         <v>466.0</v>
       </c>
       <c r="B467" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="C467" t="s">
-        <v>2189</v>
+        <v>2191</v>
       </c>
       <c r="D467" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="F467">
         <v>6.282168004148E12</v>
       </c>
       <c r="G467" s="4" t="s">
-        <v>2191</v>
+        <v>2193</v>
       </c>
       <c r="J467" t="s">
         <v>16</v>
@@ -23765,7 +23770,7 @@
         <v>1.0</v>
       </c>
       <c r="M467" t="s">
-        <v>2192</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="468" ht="14.25" customHeight="1">
@@ -23773,19 +23778,19 @@
         <v>467.0</v>
       </c>
       <c r="B468" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="C468" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="D468" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="F468">
         <v>6.28114708808E11</v>
       </c>
       <c r="G468" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="J468" t="s">
         <v>16</v>
@@ -23794,7 +23799,7 @@
         <v>1.0</v>
       </c>
       <c r="M468" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="469" ht="14.25" customHeight="1">
@@ -23802,19 +23807,19 @@
         <v>468.0</v>
       </c>
       <c r="B469" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="C469" t="s">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="D469" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F469">
         <v>6.2895367328837E13</v>
       </c>
       <c r="G469" s="4" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="J469" t="s">
         <v>16</v>
@@ -23823,7 +23828,7 @@
         <v>1.0</v>
       </c>
       <c r="M469" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="470" ht="14.25" customHeight="1">
@@ -23831,19 +23836,19 @@
         <v>469.0</v>
       </c>
       <c r="B470" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="C470" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="D470" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="F470">
         <v>6.281235530006E12</v>
       </c>
       <c r="G470" s="4" t="s">
-        <v>2206</v>
+        <v>2208</v>
       </c>
       <c r="J470" t="s">
         <v>16</v>
@@ -23852,7 +23857,7 @@
         <v>1.0</v>
       </c>
       <c r="M470" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="471" ht="14.25" customHeight="1">
@@ -23860,19 +23865,19 @@
         <v>470.0</v>
       </c>
       <c r="B471" t="s">
-        <v>2208</v>
+        <v>2210</v>
       </c>
       <c r="C471" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="D471" t="s">
-        <v>2210</v>
+        <v>2212</v>
       </c>
       <c r="F471">
         <v>6.281332363268E12</v>
       </c>
       <c r="G471" s="4" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="J471" t="s">
         <v>16</v>
@@ -23881,7 +23886,7 @@
         <v>1.0</v>
       </c>
       <c r="M471" t="s">
-        <v>2212</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="472" ht="14.25" customHeight="1">
@@ -23889,28 +23894,28 @@
         <v>471.0</v>
       </c>
       <c r="B472" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="C472" t="s">
-        <v>2214</v>
+        <v>2216</v>
       </c>
       <c r="D472" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="F472">
         <v>6.288297492872E12</v>
       </c>
       <c r="G472" s="4" t="s">
-        <v>2216</v>
+        <v>2218</v>
       </c>
       <c r="J472" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="K472">
         <v>0.0</v>
       </c>
       <c r="M472" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="473" ht="14.25" customHeight="1">
@@ -23918,19 +23923,19 @@
         <v>472.0</v>
       </c>
       <c r="B473" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="C473" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="D473" t="s">
-        <v>2220</v>
+        <v>2222</v>
       </c>
       <c r="F473">
         <v>6.288987049074E12</v>
       </c>
       <c r="G473" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="J473" t="s">
         <v>16</v>
@@ -23939,7 +23944,7 @@
         <v>1.0</v>
       </c>
       <c r="M473" t="s">
-        <v>2222</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="474" ht="14.25" customHeight="1">
@@ -23947,19 +23952,19 @@
         <v>473.0</v>
       </c>
       <c r="B474" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="C474" t="s">
-        <v>2224</v>
+        <v>2226</v>
       </c>
       <c r="D474" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F474">
         <v>6.28113787949E11</v>
       </c>
       <c r="G474" s="4" t="s">
-        <v>2226</v>
+        <v>2228</v>
       </c>
       <c r="J474" t="s">
         <v>16</v>
@@ -23968,7 +23973,7 @@
         <v>1.0</v>
       </c>
       <c r="M474" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="475" ht="14.25" customHeight="1">
@@ -23976,19 +23981,19 @@
         <v>474.0</v>
       </c>
       <c r="B475" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="C475" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="D475" t="s">
-        <v>2230</v>
+        <v>2232</v>
       </c>
       <c r="F475">
         <v>6.289523430308E12</v>
       </c>
       <c r="G475" s="4" t="s">
-        <v>2231</v>
+        <v>2233</v>
       </c>
       <c r="J475" t="s">
         <v>16</v>
@@ -23997,7 +24002,7 @@
         <v>1.0</v>
       </c>
       <c r="M475" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="476" ht="14.25" customHeight="1">
@@ -24005,19 +24010,19 @@
         <v>475.0</v>
       </c>
       <c r="B476" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
       <c r="C476" t="s">
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="D476" t="s">
-        <v>2235</v>
+        <v>2237</v>
       </c>
       <c r="F476">
         <v>6.285100779477E12</v>
       </c>
       <c r="G476" s="4" t="s">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="J476" t="s">
         <v>16</v>
@@ -24026,7 +24031,7 @@
         <v>1.0</v>
       </c>
       <c r="M476" t="s">
-        <v>2237</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="477" ht="14.25" customHeight="1">
@@ -24034,19 +24039,19 @@
         <v>476.0</v>
       </c>
       <c r="B477" t="s">
-        <v>2238</v>
+        <v>2240</v>
       </c>
       <c r="C477" t="s">
-        <v>2239</v>
+        <v>2241</v>
       </c>
       <c r="D477" t="s">
-        <v>2240</v>
+        <v>2242</v>
       </c>
       <c r="F477">
         <v>6.285852170397E12</v>
       </c>
       <c r="G477" s="4" t="s">
-        <v>2241</v>
+        <v>2243</v>
       </c>
       <c r="J477" t="s">
         <v>16</v>
@@ -24055,7 +24060,7 @@
         <v>1.0</v>
       </c>
       <c r="M477" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="478" ht="14.25" customHeight="1">
@@ -24063,19 +24068,19 @@
         <v>477.0</v>
       </c>
       <c r="B478" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="C478" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="D478" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="F478">
         <v>6.285214138886E12</v>
       </c>
       <c r="G478" s="4" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="J478" t="s">
         <v>16</v>
@@ -24084,7 +24089,7 @@
         <v>1.0</v>
       </c>
       <c r="M478" t="s">
-        <v>2247</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="479" ht="14.25" customHeight="1">
@@ -24092,19 +24097,19 @@
         <v>478.0</v>
       </c>
       <c r="B479" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="C479" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="D479" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="F479">
         <v>6.28121307296E12</v>
       </c>
       <c r="G479" s="4" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
       <c r="J479" t="s">
         <v>16</v>
@@ -24113,7 +24118,7 @@
         <v>1.0</v>
       </c>
       <c r="M479" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="480" ht="14.25" customHeight="1">
@@ -24121,19 +24126,19 @@
         <v>479.0</v>
       </c>
       <c r="B480" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="C480" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="D480" t="s">
-        <v>2255</v>
+        <v>2257</v>
       </c>
       <c r="F480">
         <v>6.2811369999E10</v>
       </c>
       <c r="G480" s="4" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
       <c r="J480" t="s">
         <v>16</v>
@@ -24142,7 +24147,7 @@
         <v>1.0</v>
       </c>
       <c r="M480" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="481" ht="14.25" customHeight="1">
@@ -24150,19 +24155,19 @@
         <v>480.0</v>
       </c>
       <c r="B481" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="C481" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
       <c r="D481" t="s">
-        <v>2260</v>
+        <v>2262</v>
       </c>
       <c r="F481">
         <v>6.287716964677E12</v>
       </c>
       <c r="G481" s="4" t="s">
-        <v>2261</v>
+        <v>2263</v>
       </c>
       <c r="J481" t="s">
         <v>16</v>
@@ -24171,7 +24176,7 @@
         <v>1.0</v>
       </c>
       <c r="M481" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="482" ht="14.25" customHeight="1">
@@ -24179,19 +24184,19 @@
         <v>481.0</v>
       </c>
       <c r="B482" t="s">
-        <v>2263</v>
+        <v>2265</v>
       </c>
       <c r="C482" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="D482" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
       <c r="F482">
         <v>6.285849090625E12</v>
       </c>
       <c r="G482" s="4" t="s">
-        <v>2266</v>
+        <v>2268</v>
       </c>
       <c r="J482" t="s">
         <v>16</v>
@@ -24200,7 +24205,7 @@
         <v>1.0</v>
       </c>
       <c r="M482" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="483" ht="14.25" customHeight="1">
@@ -24208,19 +24213,19 @@
         <v>482.0</v>
       </c>
       <c r="B483" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="C483" t="s">
-        <v>2269</v>
+        <v>2271</v>
       </c>
       <c r="D483" t="s">
-        <v>2270</v>
+        <v>2272</v>
       </c>
       <c r="F483">
         <v>6.281216785555E12</v>
       </c>
       <c r="G483" s="4" t="s">
-        <v>2271</v>
+        <v>2273</v>
       </c>
       <c r="J483" t="s">
         <v>16</v>
@@ -24229,7 +24234,7 @@
         <v>1.0</v>
       </c>
       <c r="M483" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="484" ht="14.25" customHeight="1">
@@ -24237,28 +24242,28 @@
         <v>483.0</v>
       </c>
       <c r="B484" t="s">
-        <v>2273</v>
+        <v>2275</v>
       </c>
       <c r="C484" t="s">
-        <v>2274</v>
+        <v>2276</v>
       </c>
       <c r="D484" t="s">
-        <v>2275</v>
+        <v>2277</v>
       </c>
       <c r="F484">
         <v>6.282282159795E12</v>
       </c>
       <c r="G484" s="4" t="s">
-        <v>2276</v>
+        <v>2278</v>
       </c>
       <c r="J484" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K484">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M484" t="s">
-        <v>2277</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="485" ht="14.25" customHeight="1">
@@ -24266,19 +24271,19 @@
         <v>484.0</v>
       </c>
       <c r="B485" t="s">
-        <v>2278</v>
+        <v>2280</v>
       </c>
       <c r="C485" t="s">
-        <v>2279</v>
+        <v>2281</v>
       </c>
       <c r="D485" t="s">
-        <v>2280</v>
+        <v>2282</v>
       </c>
       <c r="F485">
         <v>6.282292084304E12</v>
       </c>
       <c r="G485" s="4" t="s">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="J485" t="s">
         <v>16</v>
@@ -24287,7 +24292,7 @@
         <v>1.0</v>
       </c>
       <c r="M485" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="486" ht="14.25" customHeight="1">
@@ -24295,19 +24300,19 @@
         <v>485.0</v>
       </c>
       <c r="B486" t="s">
-        <v>2283</v>
+        <v>2285</v>
       </c>
       <c r="C486" t="s">
-        <v>2284</v>
+        <v>2286</v>
       </c>
       <c r="D486" t="s">
-        <v>2285</v>
+        <v>2287</v>
       </c>
       <c r="F486">
         <v>6.289611111172E12</v>
       </c>
       <c r="G486" s="4" t="s">
-        <v>2286</v>
+        <v>2288</v>
       </c>
       <c r="J486" t="s">
         <v>16</v>
@@ -24316,7 +24321,7 @@
         <v>1.0</v>
       </c>
       <c r="M486" t="s">
-        <v>2287</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="487" ht="14.25" customHeight="1">
@@ -24324,19 +24329,19 @@
         <v>486.0</v>
       </c>
       <c r="B487" t="s">
-        <v>2288</v>
+        <v>2290</v>
       </c>
       <c r="C487" t="s">
-        <v>2289</v>
+        <v>2291</v>
       </c>
       <c r="D487" t="s">
-        <v>2290</v>
+        <v>2292</v>
       </c>
       <c r="F487">
         <v>6.281348988689E12</v>
       </c>
       <c r="G487" s="4" t="s">
-        <v>2291</v>
+        <v>2293</v>
       </c>
       <c r="J487" t="s">
         <v>16</v>
@@ -24345,7 +24350,7 @@
         <v>1.0</v>
       </c>
       <c r="M487" t="s">
-        <v>2292</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="488" ht="14.25" customHeight="1">
@@ -24353,19 +24358,19 @@
         <v>487.0</v>
       </c>
       <c r="B488" t="s">
-        <v>2293</v>
+        <v>2295</v>
       </c>
       <c r="C488" t="s">
-        <v>2294</v>
+        <v>2296</v>
       </c>
       <c r="D488" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="F488">
         <v>6.281216393954E12</v>
       </c>
       <c r="G488" s="4" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="J488" t="s">
         <v>16</v>
@@ -24374,7 +24379,7 @@
         <v>1.0</v>
       </c>
       <c r="M488" t="s">
-        <v>2297</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="489" ht="14.25" customHeight="1">
@@ -24382,19 +24387,19 @@
         <v>488.0</v>
       </c>
       <c r="B489" t="s">
-        <v>2298</v>
+        <v>2300</v>
       </c>
       <c r="C489" t="s">
-        <v>2299</v>
+        <v>2301</v>
       </c>
       <c r="D489" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="F489">
         <v>6.289636851505E12</v>
       </c>
       <c r="G489" s="4" t="s">
-        <v>2301</v>
+        <v>2303</v>
       </c>
       <c r="J489" t="s">
         <v>16</v>
@@ -24403,7 +24408,7 @@
         <v>1.0</v>
       </c>
       <c r="M489" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="490" ht="14.25" customHeight="1">
@@ -24411,19 +24416,19 @@
         <v>489.0</v>
       </c>
       <c r="B490" t="s">
-        <v>2303</v>
+        <v>2305</v>
       </c>
       <c r="C490" t="s">
-        <v>2304</v>
+        <v>2306</v>
       </c>
       <c r="D490" t="s">
-        <v>2305</v>
+        <v>2307</v>
       </c>
       <c r="F490">
         <v>6.281235873852E12</v>
       </c>
       <c r="G490" s="4" t="s">
-        <v>2306</v>
+        <v>2308</v>
       </c>
       <c r="J490" t="s">
         <v>16</v>
@@ -24432,7 +24437,7 @@
         <v>1.0</v>
       </c>
       <c r="M490" t="s">
-        <v>2307</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="491" ht="14.25" customHeight="1">
@@ -24440,19 +24445,19 @@
         <v>490.0</v>
       </c>
       <c r="B491" t="s">
-        <v>2308</v>
+        <v>2310</v>
       </c>
       <c r="C491" t="s">
-        <v>2309</v>
+        <v>2311</v>
       </c>
       <c r="D491" t="s">
-        <v>2310</v>
+        <v>2312</v>
       </c>
       <c r="F491">
         <v>6.281315823519E12</v>
       </c>
       <c r="G491" s="4" t="s">
-        <v>2311</v>
+        <v>2313</v>
       </c>
       <c r="J491" t="s">
         <v>107</v>
@@ -24461,7 +24466,7 @@
         <v>0.0</v>
       </c>
       <c r="M491" t="s">
-        <v>2312</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="492" ht="14.25" customHeight="1">
@@ -24469,19 +24474,19 @@
         <v>491.0</v>
       </c>
       <c r="B492" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
       <c r="C492" t="s">
-        <v>2314</v>
+        <v>2316</v>
       </c>
       <c r="D492" t="s">
-        <v>2315</v>
+        <v>2317</v>
       </c>
       <c r="F492">
         <v>6.281252793335E12</v>
       </c>
       <c r="G492" s="4" t="s">
-        <v>2316</v>
+        <v>2318</v>
       </c>
       <c r="J492" t="s">
         <v>16</v>
@@ -24490,7 +24495,7 @@
         <v>1.0</v>
       </c>
       <c r="M492" t="s">
-        <v>2317</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="493" ht="14.25" customHeight="1">
@@ -24498,19 +24503,19 @@
         <v>492.0</v>
       </c>
       <c r="B493" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="C493" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
       <c r="D493" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="F493">
         <v>6.285854652368E12</v>
       </c>
       <c r="G493" s="4" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
       <c r="J493" t="s">
         <v>16</v>
@@ -24519,10 +24524,10 @@
         <v>1.0</v>
       </c>
       <c r="L493" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
       <c r="M493" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="494" ht="14.25" customHeight="1">
@@ -24530,19 +24535,19 @@
         <v>493.0</v>
       </c>
       <c r="B494" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="C494" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
       <c r="D494" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="F494">
         <v>6.282216301514E12</v>
       </c>
       <c r="G494" s="4" t="s">
-        <v>2327</v>
+        <v>2329</v>
       </c>
       <c r="J494" t="s">
         <v>16</v>
@@ -24551,7 +24556,7 @@
         <v>1.0</v>
       </c>
       <c r="M494" t="s">
-        <v>2328</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="495" ht="14.25" customHeight="1">
@@ -24559,19 +24564,19 @@
         <v>494.0</v>
       </c>
       <c r="B495" t="s">
-        <v>2329</v>
+        <v>2331</v>
       </c>
       <c r="C495" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
       <c r="D495" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
       <c r="F495">
         <v>6.28961411634E12</v>
       </c>
       <c r="G495" s="4" t="s">
-        <v>2332</v>
+        <v>2334</v>
       </c>
       <c r="J495" t="s">
         <v>16</v>
@@ -24580,7 +24585,7 @@
         <v>1.0</v>
       </c>
       <c r="M495" t="s">
-        <v>2333</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="496" ht="14.25" customHeight="1">
@@ -24588,19 +24593,19 @@
         <v>495.0</v>
       </c>
       <c r="B496" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="C496" t="s">
-        <v>2335</v>
+        <v>2337</v>
       </c>
       <c r="D496" t="s">
-        <v>2336</v>
+        <v>2338</v>
       </c>
       <c r="F496">
         <v>6.281152975E11</v>
       </c>
       <c r="G496" s="4" t="s">
-        <v>2337</v>
+        <v>2339</v>
       </c>
       <c r="J496" t="s">
         <v>16</v>
@@ -24609,7 +24614,7 @@
         <v>1.0</v>
       </c>
       <c r="M496" t="s">
-        <v>2338</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="497" ht="14.25" customHeight="1">
@@ -24617,19 +24622,19 @@
         <v>496.0</v>
       </c>
       <c r="B497" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
       <c r="C497" t="s">
-        <v>2340</v>
+        <v>2342</v>
       </c>
       <c r="D497" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="F497">
         <v>6.2895630917666E13</v>
       </c>
       <c r="G497" s="4" t="s">
-        <v>2342</v>
+        <v>2344</v>
       </c>
       <c r="J497" t="s">
         <v>16</v>
@@ -24638,7 +24643,7 @@
         <v>1.0</v>
       </c>
       <c r="M497" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="498" ht="14.25" customHeight="1">
@@ -24646,19 +24651,19 @@
         <v>497.0</v>
       </c>
       <c r="B498" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
       <c r="C498" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="D498" t="s">
-        <v>2346</v>
+        <v>2348</v>
       </c>
       <c r="F498">
         <v>6.2895061872E12</v>
       </c>
       <c r="G498" s="4" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="J498" t="s">
         <v>16</v>
@@ -24667,7 +24672,7 @@
         <v>1.0</v>
       </c>
       <c r="M498" t="s">
-        <v>2348</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="499" ht="14.25" customHeight="1">
@@ -24675,19 +24680,19 @@
         <v>498.0</v>
       </c>
       <c r="B499" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="C499" t="s">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="D499" t="s">
-        <v>2351</v>
+        <v>2353</v>
       </c>
       <c r="F499">
         <v>6.281336862624E12</v>
       </c>
       <c r="G499" s="4" t="s">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="J499" t="s">
         <v>16</v>
@@ -24696,7 +24701,7 @@
         <v>1.0</v>
       </c>
       <c r="M499" t="s">
-        <v>2353</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="500" ht="14.25" customHeight="1">
@@ -24704,19 +24709,19 @@
         <v>499.0</v>
       </c>
       <c r="B500" t="s">
-        <v>2354</v>
+        <v>2356</v>
       </c>
       <c r="C500" t="s">
-        <v>2355</v>
+        <v>2357</v>
       </c>
       <c r="D500" t="s">
-        <v>2356</v>
+        <v>2358</v>
       </c>
       <c r="F500">
         <v>6.288743627148E13</v>
       </c>
       <c r="G500" s="4" t="s">
-        <v>2357</v>
+        <v>2359</v>
       </c>
       <c r="J500" t="s">
         <v>16</v>
@@ -24725,7 +24730,7 @@
         <v>1.0</v>
       </c>
       <c r="M500" t="s">
-        <v>2358</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="501" ht="14.25" customHeight="1">
@@ -24733,28 +24738,28 @@
         <v>500.0</v>
       </c>
       <c r="B501" t="s">
-        <v>2359</v>
+        <v>2361</v>
       </c>
       <c r="C501" t="s">
-        <v>2360</v>
+        <v>2362</v>
       </c>
       <c r="D501" t="s">
-        <v>2361</v>
+        <v>2363</v>
       </c>
       <c r="F501">
         <v>6.281231899995E12</v>
       </c>
       <c r="G501" s="4" t="s">
-        <v>2362</v>
+        <v>2364</v>
       </c>
       <c r="J501" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K501">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M501" t="s">
-        <v>2363</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="502" ht="14.25" customHeight="1">
@@ -24762,19 +24767,19 @@
         <v>501.0</v>
       </c>
       <c r="B502" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
       <c r="C502" t="s">
-        <v>2365</v>
+        <v>2367</v>
       </c>
       <c r="D502" t="s">
-        <v>2366</v>
+        <v>2368</v>
       </c>
       <c r="F502">
         <v>6.281346544599E12</v>
       </c>
       <c r="G502" s="4" t="s">
-        <v>2367</v>
+        <v>2369</v>
       </c>
       <c r="J502" t="s">
         <v>16</v>
@@ -24783,7 +24788,7 @@
         <v>1.0</v>
       </c>
       <c r="M502" t="s">
-        <v>2368</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="503" ht="14.25" customHeight="1">
@@ -24791,19 +24796,19 @@
         <v>502.0</v>
       </c>
       <c r="B503" t="s">
-        <v>2369</v>
+        <v>2371</v>
       </c>
       <c r="C503" t="s">
-        <v>2370</v>
+        <v>2372</v>
       </c>
       <c r="D503" t="s">
-        <v>2371</v>
+        <v>2373</v>
       </c>
       <c r="F503">
         <v>6.282179134503E12</v>
       </c>
       <c r="G503" s="4" t="s">
-        <v>2372</v>
+        <v>2374</v>
       </c>
       <c r="J503" t="s">
         <v>16</v>
@@ -24812,7 +24817,7 @@
         <v>1.0</v>
       </c>
       <c r="M503" t="s">
-        <v>2373</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="504" ht="14.25" customHeight="1">
@@ -24820,19 +24825,19 @@
         <v>503.0</v>
       </c>
       <c r="B504" t="s">
-        <v>2374</v>
+        <v>2376</v>
       </c>
       <c r="C504" t="s">
-        <v>2375</v>
+        <v>2377</v>
       </c>
       <c r="D504" t="s">
-        <v>2376</v>
+        <v>2378</v>
       </c>
       <c r="F504">
         <v>6.28155493848E12</v>
       </c>
       <c r="G504" s="4" t="s">
-        <v>2377</v>
+        <v>2379</v>
       </c>
       <c r="J504" t="s">
         <v>16</v>
@@ -24841,7 +24846,7 @@
         <v>1.0</v>
       </c>
       <c r="M504" t="s">
-        <v>2378</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="505" ht="14.25" customHeight="1">
@@ -24849,19 +24854,19 @@
         <v>504.0</v>
       </c>
       <c r="B505" t="s">
-        <v>2379</v>
+        <v>2381</v>
       </c>
       <c r="C505" t="s">
-        <v>2380</v>
+        <v>2382</v>
       </c>
       <c r="D505" t="s">
-        <v>2381</v>
+        <v>2383</v>
       </c>
       <c r="F505">
         <v>6.28898900389E12</v>
       </c>
       <c r="G505" s="4" t="s">
-        <v>2382</v>
+        <v>2384</v>
       </c>
       <c r="J505" t="s">
         <v>16</v>
@@ -24870,7 +24875,7 @@
         <v>1.0</v>
       </c>
       <c r="M505" t="s">
-        <v>2383</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="506" ht="14.25" customHeight="1">
@@ -24878,19 +24883,19 @@
         <v>505.0</v>
       </c>
       <c r="B506" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
       <c r="C506" t="s">
-        <v>2385</v>
+        <v>2387</v>
       </c>
       <c r="D506" t="s">
-        <v>2386</v>
+        <v>2388</v>
       </c>
       <c r="F506">
         <v>6.28880594372E12</v>
       </c>
       <c r="G506" s="4" t="s">
-        <v>2387</v>
+        <v>2389</v>
       </c>
       <c r="J506" t="s">
         <v>16</v>
@@ -24899,7 +24904,7 @@
         <v>1.0</v>
       </c>
       <c r="M506" t="s">
-        <v>2388</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="507" ht="14.25" customHeight="1">
@@ -24907,19 +24912,19 @@
         <v>506.0</v>
       </c>
       <c r="B507" t="s">
-        <v>2389</v>
+        <v>2391</v>
       </c>
       <c r="C507" t="s">
-        <v>2390</v>
+        <v>2392</v>
       </c>
       <c r="D507" t="s">
-        <v>2391</v>
+        <v>2393</v>
       </c>
       <c r="F507">
         <v>6.285736562777E12</v>
       </c>
       <c r="G507" s="4" t="s">
-        <v>2392</v>
+        <v>2394</v>
       </c>
       <c r="J507" t="s">
         <v>16</v>
@@ -24928,7 +24933,7 @@
         <v>1.0</v>
       </c>
       <c r="M507" t="s">
-        <v>2393</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="508" ht="14.25" customHeight="1">
@@ -24936,19 +24941,19 @@
         <v>507.0</v>
       </c>
       <c r="B508" t="s">
-        <v>2394</v>
+        <v>2396</v>
       </c>
       <c r="C508" t="s">
-        <v>2395</v>
+        <v>2397</v>
       </c>
       <c r="D508" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="F508">
         <v>6.285961456625E12</v>
       </c>
       <c r="G508" s="4" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
       <c r="J508" t="s">
         <v>107</v>
@@ -24957,7 +24962,7 @@
         <v>0.0</v>
       </c>
       <c r="M508" t="s">
-        <v>2398</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="509" ht="14.25" customHeight="1">
@@ -24965,19 +24970,19 @@
         <v>508.0</v>
       </c>
       <c r="B509" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="C509" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
       <c r="D509" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
       <c r="F509">
         <v>6.2899091801E11</v>
       </c>
       <c r="G509" s="4" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
       <c r="J509" t="s">
         <v>16</v>
@@ -24986,7 +24991,7 @@
         <v>1.0</v>
       </c>
       <c r="M509" t="s">
-        <v>2403</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="510" ht="14.25" customHeight="1">
@@ -24994,19 +24999,19 @@
         <v>509.0</v>
       </c>
       <c r="B510" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
       <c r="C510" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
       <c r="D510" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="F510">
         <v>6.282251311399E12</v>
       </c>
       <c r="G510" s="4" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
       <c r="J510" t="s">
         <v>16</v>
@@ -25015,7 +25020,7 @@
         <v>1.0</v>
       </c>
       <c r="M510" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="511" ht="14.25" customHeight="1">
@@ -25023,19 +25028,19 @@
         <v>510.0</v>
       </c>
       <c r="B511" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="C511" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="D511" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
       <c r="F511">
         <v>6.289697122116E12</v>
       </c>
       <c r="G511" s="4" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="J511" t="s">
         <v>16</v>
@@ -25044,7 +25049,7 @@
         <v>1.0</v>
       </c>
       <c r="M511" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="512" ht="14.25" customHeight="1">
@@ -25052,19 +25057,19 @@
         <v>511.0</v>
       </c>
       <c r="B512" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
       <c r="C512" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="D512" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
       <c r="F512">
         <v>6.282197996123E12</v>
       </c>
       <c r="G512" s="4" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="J512" t="s">
         <v>16</v>
@@ -25073,7 +25078,7 @@
         <v>1.0</v>
       </c>
       <c r="M512" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="513" ht="14.25" customHeight="1">
@@ -25081,19 +25086,19 @@
         <v>512.0</v>
       </c>
       <c r="B513" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="C513" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D513" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="F513">
         <v>6.282326573338E12</v>
       </c>
       <c r="G513" s="4" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="J513" t="s">
         <v>107</v>
@@ -25102,7 +25107,7 @@
         <v>0.0</v>
       </c>
       <c r="M513" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="514" ht="14.25" customHeight="1">
@@ -25110,19 +25115,19 @@
         <v>513.0</v>
       </c>
       <c r="B514" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="C514" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="D514" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="F514">
         <v>6.282310812402E12</v>
       </c>
       <c r="G514" s="4" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="J514" t="s">
         <v>16</v>
@@ -25131,7 +25136,7 @@
         <v>1.0</v>
       </c>
       <c r="M514" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="515" ht="14.25" customHeight="1">
@@ -25139,19 +25144,19 @@
         <v>514.0</v>
       </c>
       <c r="B515" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="C515" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="D515" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="F515">
         <v>6.281240576677E12</v>
       </c>
       <c r="G515" s="4" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
       <c r="J515" t="s">
         <v>16</v>
@@ -25160,7 +25165,7 @@
         <v>1.0</v>
       </c>
       <c r="M515" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="516" ht="14.25" customHeight="1">
@@ -25168,19 +25173,19 @@
         <v>515.0</v>
       </c>
       <c r="B516" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="C516" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="D516" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
       <c r="F516">
         <v>6.289697081524E12</v>
       </c>
       <c r="G516" s="4" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
       <c r="J516" t="s">
         <v>16</v>
@@ -25189,7 +25194,7 @@
         <v>1.0</v>
       </c>
       <c r="M516" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="517" ht="14.25" customHeight="1">
@@ -25197,19 +25202,19 @@
         <v>516.0</v>
       </c>
       <c r="B517" t="s">
-        <v>2439</v>
+        <v>2441</v>
       </c>
       <c r="C517" t="s">
-        <v>2440</v>
+        <v>2442</v>
       </c>
       <c r="D517" t="s">
-        <v>2441</v>
+        <v>2443</v>
       </c>
       <c r="F517">
         <v>6.282370050222E12</v>
       </c>
       <c r="G517" s="4" t="s">
-        <v>2442</v>
+        <v>2444</v>
       </c>
       <c r="J517" t="s">
         <v>16</v>
@@ -25218,7 +25223,7 @@
         <v>1.0</v>
       </c>
       <c r="M517" t="s">
-        <v>2443</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="518" ht="14.25" customHeight="1">
@@ -25226,19 +25231,19 @@
         <v>517.0</v>
       </c>
       <c r="B518" t="s">
-        <v>2444</v>
+        <v>2446</v>
       </c>
       <c r="C518" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="D518" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
       <c r="F518">
         <v>6.281335480807E12</v>
       </c>
       <c r="G518" s="4" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="J518" t="s">
         <v>16</v>
@@ -25247,7 +25252,7 @@
         <v>1.0</v>
       </c>
       <c r="M518" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="519" ht="14.25" customHeight="1">
@@ -25255,19 +25260,19 @@
         <v>518.0</v>
       </c>
       <c r="B519" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="C519" t="s">
-        <v>2450</v>
+        <v>2452</v>
       </c>
       <c r="D519" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="F519">
         <v>6.285755160106E12</v>
       </c>
       <c r="G519" s="4" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="J519" t="s">
         <v>16</v>
@@ -25276,7 +25281,7 @@
         <v>1.0</v>
       </c>
       <c r="M519" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="520" ht="14.25" customHeight="1">
@@ -25284,19 +25289,19 @@
         <v>519.0</v>
       </c>
       <c r="B520" t="s">
-        <v>2454</v>
+        <v>2456</v>
       </c>
       <c r="C520" t="s">
-        <v>2455</v>
+        <v>2457</v>
       </c>
       <c r="D520" t="s">
-        <v>2456</v>
+        <v>2458</v>
       </c>
       <c r="F520">
         <v>6.282136620798E12</v>
       </c>
       <c r="G520" s="4" t="s">
-        <v>2457</v>
+        <v>2459</v>
       </c>
       <c r="J520" t="s">
         <v>16</v>
@@ -25305,7 +25310,7 @@
         <v>1.0</v>
       </c>
       <c r="M520" t="s">
-        <v>2458</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="521" ht="14.25" customHeight="1">
@@ -25313,19 +25318,19 @@
         <v>520.0</v>
       </c>
       <c r="B521" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="C521" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
       <c r="D521" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
       <c r="F521">
         <v>6.281334071718E12</v>
       </c>
       <c r="G521" s="4" t="s">
-        <v>2462</v>
+        <v>2464</v>
       </c>
       <c r="J521" t="s">
         <v>26</v>
@@ -25334,7 +25339,7 @@
         <v>0.0</v>
       </c>
       <c r="M521" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
     </row>
   </sheetData>
